--- a/projetos/gestao-ia-planilhas/produto/kit-essencial/entrega/02-relatorio-mensal-pronto.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-essencial/entrega/02-relatorio-mensal-pronto.xlsx
@@ -953,9 +953,9 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5">
+      <c r="A1" s="5" t="str">
         <f>Config!B4&amp;" · Relatório de "&amp;Config!B6&amp;" de "&amp;Config!B5</f>
-        <v/>
+        <v>Prisma Comunicação (exemplo fictício) · Relatório de Setembro de 2026</v>
       </c>
     </row>
     <row r="2">
@@ -1013,45 +1013,45 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8">
+      <c r="A5" s="8" t="str">
         <f>IF(Indicadores!A5="","",Indicadores!A5)</f>
-        <v/>
+        <v>Receita</v>
       </c>
       <c r="B5" s="9">
         <f>IF(Indicadores!A5="","",IF(INDEX(Indicadores!$F5:$Q5,Config!$B$7)="","",INDEX(Indicadores!$F5:$Q5,Config!$B$7)))</f>
-        <v/>
+        <v>131200</v>
       </c>
       <c r="C5" s="9">
         <f>IF(OR(Indicadores!A5="",Config!$B$7=1),"",IF(INDEX(Indicadores!$F5:$Q5,Config!$B$7-1)="","",INDEX(Indicadores!$F5:$Q5,Config!$B$7-1)))</f>
-        <v/>
+        <v>124600</v>
       </c>
       <c r="D5" s="10">
         <f>IF(OR(B5="",C5="",C5=0),"",(B5-C5)/ABS(C5))</f>
-        <v/>
+        <v>0.0529695024077047</v>
       </c>
       <c r="E5" s="9">
         <f>IF(OR(Indicadores!A5="",Indicadores!D5=""),"",Indicadores!D5)</f>
-        <v/>
+        <v>120000</v>
       </c>
       <c r="F5" s="10">
         <f>IF(OR(B5="",E5="",E5=0),"",(B5-E5)/ABS(E5))</f>
-        <v/>
-      </c>
-      <c r="G5" s="11">
+        <v>0.0933333333333333</v>
+      </c>
+      <c r="G5" s="11" t="str">
         <f>IF(OR(B5="",E5=""),"",IF(Indicadores!E5="Não",IF(B5&lt;=E5,"No alvo","Acima da meta"),IF(B5&gt;=E5,"No alvo","Abaixo da meta")))</f>
-        <v/>
+        <v>No alvo</v>
       </c>
       <c r="H5" s="9">
         <f>IF(Indicadores!A5="","",Indicadores!R5)</f>
-        <v/>
-      </c>
-      <c r="I5" s="11">
+        <v>1033600</v>
+      </c>
+      <c r="I5" s="11" t="str">
         <f>IF(Indicadores!A5="","",Indicadores!B5)</f>
-        <v/>
+        <v>R$</v>
       </c>
       <c r="N5" s="12">
         <f>IF(Indicadores!C5="",2,Indicadores!C5)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O5" s="12">
         <f>IF(OR(F5="",G5="",G5="No alvo"),"",IF(Indicadores!E5="Não",F5,-F5))</f>
@@ -1059,91 +1059,91 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8">
+      <c r="A6" s="8" t="str">
         <f>IF(Indicadores!A6="","",Indicadores!A6)</f>
-        <v/>
+        <v>Despesas</v>
       </c>
       <c r="B6" s="9">
         <f>IF(Indicadores!A6="","",IF(INDEX(Indicadores!$F6:$Q6,Config!$B$7)="","",INDEX(Indicadores!$F6:$Q6,Config!$B$7)))</f>
-        <v/>
+        <v>89800</v>
       </c>
       <c r="C6" s="9">
         <f>IF(OR(Indicadores!A6="",Config!$B$7=1),"",IF(INDEX(Indicadores!$F6:$Q6,Config!$B$7-1)="","",INDEX(Indicadores!$F6:$Q6,Config!$B$7-1)))</f>
-        <v/>
+        <v>87300</v>
       </c>
       <c r="D6" s="10">
         <f>IF(OR(B6="",C6="",C6=0),"",(B6-C6)/ABS(C6))</f>
-        <v/>
+        <v>0.0286368843069874</v>
       </c>
       <c r="E6" s="9">
         <f>IF(OR(Indicadores!A6="",Indicadores!D6=""),"",Indicadores!D6)</f>
-        <v/>
+        <v>85000</v>
       </c>
       <c r="F6" s="10">
         <f>IF(OR(B6="",E6="",E6=0),"",(B6-E6)/ABS(E6))</f>
-        <v/>
-      </c>
-      <c r="G6" s="11">
+        <v>0.0564705882352941</v>
+      </c>
+      <c r="G6" s="11" t="str">
         <f>IF(OR(B6="",E6=""),"",IF(Indicadores!E6="Não",IF(B6&lt;=E6,"No alvo","Acima da meta"),IF(B6&gt;=E6,"No alvo","Abaixo da meta")))</f>
-        <v/>
+        <v>Acima da meta</v>
       </c>
       <c r="H6" s="9">
         <f>IF(Indicadores!A6="","",Indicadores!R6)</f>
-        <v/>
-      </c>
-      <c r="I6" s="11">
+        <v>766600</v>
+      </c>
+      <c r="I6" s="11" t="str">
         <f>IF(Indicadores!A6="","",Indicadores!B6)</f>
-        <v/>
+        <v>R$</v>
       </c>
       <c r="N6" s="12">
         <f>IF(Indicadores!C6="",2,Indicadores!C6)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O6" s="12">
         <f>IF(OR(F6="",G6="",G6="No alvo"),"",IF(Indicadores!E6="Não",F6,-F6))</f>
-        <v/>
+        <v>0.0564705882352941</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8">
+      <c r="A7" s="8" t="str">
         <f>IF(Indicadores!A7="","",Indicadores!A7)</f>
-        <v/>
+        <v>Resultado (receita - despesas)</v>
       </c>
       <c r="B7" s="9">
         <f>IF(Indicadores!A7="","",IF(INDEX(Indicadores!$F7:$Q7,Config!$B$7)="","",INDEX(Indicadores!$F7:$Q7,Config!$B$7)))</f>
-        <v/>
+        <v>41400</v>
       </c>
       <c r="C7" s="9">
         <f>IF(OR(Indicadores!A7="",Config!$B$7=1),"",IF(INDEX(Indicadores!$F7:$Q7,Config!$B$7-1)="","",INDEX(Indicadores!$F7:$Q7,Config!$B$7-1)))</f>
-        <v/>
+        <v>37300</v>
       </c>
       <c r="D7" s="10">
         <f>IF(OR(B7="",C7="",C7=0),"",(B7-C7)/ABS(C7))</f>
-        <v/>
+        <v>0.109919571045576</v>
       </c>
       <c r="E7" s="9">
         <f>IF(OR(Indicadores!A7="",Indicadores!D7=""),"",Indicadores!D7)</f>
-        <v/>
+        <v>35000</v>
       </c>
       <c r="F7" s="10">
         <f>IF(OR(B7="",E7="",E7=0),"",(B7-E7)/ABS(E7))</f>
-        <v/>
-      </c>
-      <c r="G7" s="11">
+        <v>0.182857142857143</v>
+      </c>
+      <c r="G7" s="11" t="str">
         <f>IF(OR(B7="",E7=""),"",IF(Indicadores!E7="Não",IF(B7&lt;=E7,"No alvo","Acima da meta"),IF(B7&gt;=E7,"No alvo","Abaixo da meta")))</f>
-        <v/>
+        <v>No alvo</v>
       </c>
       <c r="H7" s="9">
         <f>IF(Indicadores!A7="","",Indicadores!R7)</f>
-        <v/>
-      </c>
-      <c r="I7" s="11">
+        <v>267000</v>
+      </c>
+      <c r="I7" s="11" t="str">
         <f>IF(Indicadores!A7="","",Indicadores!B7)</f>
-        <v/>
+        <v>R$</v>
       </c>
       <c r="N7" s="12">
         <f>IF(Indicadores!C7="",2,Indicadores!C7)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O7" s="12">
         <f>IF(OR(F7="",G7="",G7="No alvo"),"",IF(Indicadores!E7="Não",F7,-F7))</f>
@@ -1151,45 +1151,45 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8">
+      <c r="A8" s="8" t="str">
         <f>IF(Indicadores!A8="","",Indicadores!A8)</f>
-        <v/>
+        <v>Novos clientes</v>
       </c>
       <c r="B8" s="9">
         <f>IF(Indicadores!A8="","",IF(INDEX(Indicadores!$F8:$Q8,Config!$B$7)="","",INDEX(Indicadores!$F8:$Q8,Config!$B$7)))</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="C8" s="9">
         <f>IF(OR(Indicadores!A8="",Config!$B$7=1),"",IF(INDEX(Indicadores!$F8:$Q8,Config!$B$7-1)="","",INDEX(Indicadores!$F8:$Q8,Config!$B$7-1)))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="D8" s="10">
         <f>IF(OR(B8="",C8="",C8=0),"",(B8-C8)/ABS(C8))</f>
-        <v/>
+        <v>-0.142857142857143</v>
       </c>
       <c r="E8" s="9">
         <f>IF(OR(Indicadores!A8="",Indicadores!D8=""),"",Indicadores!D8)</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="F8" s="10">
         <f>IF(OR(B8="",E8="",E8=0),"",(B8-E8)/ABS(E8))</f>
-        <v/>
-      </c>
-      <c r="G8" s="11">
+        <v>0</v>
+      </c>
+      <c r="G8" s="11" t="str">
         <f>IF(OR(B8="",E8=""),"",IF(Indicadores!E8="Não",IF(B8&lt;=E8,"No alvo","Acima da meta"),IF(B8&gt;=E8,"No alvo","Abaixo da meta")))</f>
-        <v/>
+        <v>No alvo</v>
       </c>
       <c r="H8" s="9">
         <f>IF(Indicadores!A8="","",Indicadores!R8)</f>
-        <v/>
-      </c>
-      <c r="I8" s="11">
+        <v>44</v>
+      </c>
+      <c r="I8" s="11" t="str">
         <f>IF(Indicadores!A8="","",Indicadores!B8)</f>
-        <v/>
+        <v>un</v>
       </c>
       <c r="N8" s="12">
         <f>IF(Indicadores!C8="",2,Indicadores!C8)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O8" s="12">
         <f>IF(OR(F8="",G8="",G8="No alvo"),"",IF(Indicadores!E8="Não",F8,-F8))</f>
@@ -1197,45 +1197,45 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8">
+      <c r="A9" s="8" t="str">
         <f>IF(Indicadores!A9="","",Indicadores!A9)</f>
-        <v/>
+        <v>Leads recebidos</v>
       </c>
       <c r="B9" s="9">
         <f>IF(Indicadores!A9="","",IF(INDEX(Indicadores!$F9:$Q9,Config!$B$7)="","",INDEX(Indicadores!$F9:$Q9,Config!$B$7)))</f>
-        <v/>
+        <v>137</v>
       </c>
       <c r="C9" s="9">
         <f>IF(OR(Indicadores!A9="",Config!$B$7=1),"",IF(INDEX(Indicadores!$F9:$Q9,Config!$B$7-1)="","",INDEX(Indicadores!$F9:$Q9,Config!$B$7-1)))</f>
-        <v/>
+        <v>142</v>
       </c>
       <c r="D9" s="10">
         <f>IF(OR(B9="",C9="",C9=0),"",(B9-C9)/ABS(C9))</f>
-        <v/>
+        <v>-0.0352112676056338</v>
       </c>
       <c r="E9" s="9">
         <f>IF(OR(Indicadores!A9="",Indicadores!D9=""),"",Indicadores!D9)</f>
-        <v/>
+        <v>120</v>
       </c>
       <c r="F9" s="10">
         <f>IF(OR(B9="",E9="",E9=0),"",(B9-E9)/ABS(E9))</f>
-        <v/>
-      </c>
-      <c r="G9" s="11">
+        <v>0.141666666666667</v>
+      </c>
+      <c r="G9" s="11" t="str">
         <f>IF(OR(B9="",E9=""),"",IF(Indicadores!E9="Não",IF(B9&lt;=E9,"No alvo","Acima da meta"),IF(B9&gt;=E9,"No alvo","Abaixo da meta")))</f>
-        <v/>
+        <v>No alvo</v>
       </c>
       <c r="H9" s="9">
         <f>IF(Indicadores!A9="","",Indicadores!R9)</f>
-        <v/>
-      </c>
-      <c r="I9" s="11">
+        <v>1032</v>
+      </c>
+      <c r="I9" s="11" t="str">
         <f>IF(Indicadores!A9="","",Indicadores!B9)</f>
-        <v/>
+        <v>un</v>
       </c>
       <c r="N9" s="12">
         <f>IF(Indicadores!C9="",2,Indicadores!C9)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O9" s="12">
         <f>IF(OR(F9="",G9="",G9="No alvo"),"",IF(Indicadores!E9="Não",F9,-F9))</f>
@@ -1243,91 +1243,91 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8">
+      <c r="A10" s="8" t="str">
         <f>IF(Indicadores!A10="","",Indicadores!A10)</f>
-        <v/>
+        <v>Taxa de conversão de leads</v>
       </c>
       <c r="B10" s="9">
         <f>IF(Indicadores!A10="","",IF(INDEX(Indicadores!$F10:$Q10,Config!$B$7)="","",INDEX(Indicadores!$F10:$Q10,Config!$B$7)))</f>
-        <v/>
+        <v>4.4</v>
       </c>
       <c r="C10" s="9">
         <f>IF(OR(Indicadores!A10="",Config!$B$7=1),"",IF(INDEX(Indicadores!$F10:$Q10,Config!$B$7-1)="","",INDEX(Indicadores!$F10:$Q10,Config!$B$7-1)))</f>
-        <v/>
+        <v>4.9</v>
       </c>
       <c r="D10" s="10">
         <f>IF(OR(B10="",C10="",C10=0),"",(B10-C10)/ABS(C10))</f>
-        <v/>
+        <v>-0.102040816326531</v>
       </c>
       <c r="E10" s="9">
         <f>IF(OR(Indicadores!A10="",Indicadores!D10=""),"",Indicadores!D10)</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="F10" s="10">
         <f>IF(OR(B10="",E10="",E10=0),"",(B10-E10)/ABS(E10))</f>
-        <v/>
-      </c>
-      <c r="G10" s="11">
+        <v>-0.12</v>
+      </c>
+      <c r="G10" s="11" t="str">
         <f>IF(OR(B10="",E10=""),"",IF(Indicadores!E10="Não",IF(B10&lt;=E10,"No alvo","Acima da meta"),IF(B10&gt;=E10,"No alvo","Abaixo da meta")))</f>
-        <v/>
+        <v>Abaixo da meta</v>
       </c>
       <c r="H10" s="9">
         <f>IF(Indicadores!A10="","",Indicadores!R10)</f>
-        <v/>
-      </c>
-      <c r="I10" s="11">
+        <v>4.2</v>
+      </c>
+      <c r="I10" s="11" t="str">
         <f>IF(Indicadores!A10="","",Indicadores!B10)</f>
-        <v/>
+        <v>%</v>
       </c>
       <c r="N10" s="12">
         <f>IF(Indicadores!C10="",2,Indicadores!C10)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="O10" s="12">
         <f>IF(OR(F10="",G10="",G10="No alvo"),"",IF(Indicadores!E10="Não",F10,-F10))</f>
-        <v/>
+        <v>0.12</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8">
+      <c r="A11" s="8" t="str">
         <f>IF(Indicadores!A11="","",Indicadores!A11)</f>
-        <v/>
+        <v>Ticket médio</v>
       </c>
       <c r="B11" s="9">
         <f>IF(Indicadores!A11="","",IF(INDEX(Indicadores!$F11:$Q11,Config!$B$7)="","",INDEX(Indicadores!$F11:$Q11,Config!$B$7)))</f>
-        <v/>
+        <v>9700</v>
       </c>
       <c r="C11" s="9">
         <f>IF(OR(Indicadores!A11="",Config!$B$7=1),"",IF(INDEX(Indicadores!$F11:$Q11,Config!$B$7-1)="","",INDEX(Indicadores!$F11:$Q11,Config!$B$7-1)))</f>
-        <v/>
+        <v>9400</v>
       </c>
       <c r="D11" s="10">
         <f>IF(OR(B11="",C11="",C11=0),"",(B11-C11)/ABS(C11))</f>
-        <v/>
+        <v>0.0319148936170213</v>
       </c>
       <c r="E11" s="9">
         <f>IF(OR(Indicadores!A11="",Indicadores!D11=""),"",Indicadores!D11)</f>
-        <v/>
+        <v>9000</v>
       </c>
       <c r="F11" s="10">
         <f>IF(OR(B11="",E11="",E11=0),"",(B11-E11)/ABS(E11))</f>
-        <v/>
-      </c>
-      <c r="G11" s="11">
+        <v>0.0777777777777778</v>
+      </c>
+      <c r="G11" s="11" t="str">
         <f>IF(OR(B11="",E11=""),"",IF(Indicadores!E11="Não",IF(B11&lt;=E11,"No alvo","Acima da meta"),IF(B11&gt;=E11,"No alvo","Abaixo da meta")))</f>
-        <v/>
+        <v>No alvo</v>
       </c>
       <c r="H11" s="9">
         <f>IF(Indicadores!A11="","",Indicadores!R11)</f>
-        <v/>
-      </c>
-      <c r="I11" s="11">
+        <v>80700</v>
+      </c>
+      <c r="I11" s="11" t="str">
         <f>IF(Indicadores!A11="","",Indicadores!B11)</f>
-        <v/>
+        <v>R$</v>
       </c>
       <c r="N11" s="12">
         <f>IF(Indicadores!C11="",2,Indicadores!C11)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O11" s="12">
         <f>IF(OR(F11="",G11="",G11="No alvo"),"",IF(Indicadores!E11="Não",F11,-F11))</f>
@@ -1335,45 +1335,45 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8">
+      <c r="A12" s="8" t="str">
         <f>IF(Indicadores!A12="","",Indicadores!A12)</f>
-        <v/>
+        <v>Inadimplência</v>
       </c>
       <c r="B12" s="9">
         <f>IF(Indicadores!A12="","",IF(INDEX(Indicadores!$F12:$Q12,Config!$B$7)="","",INDEX(Indicadores!$F12:$Q12,Config!$B$7)))</f>
-        <v/>
+        <v>2.4</v>
       </c>
       <c r="C12" s="9">
         <f>IF(OR(Indicadores!A12="",Config!$B$7=1),"",IF(INDEX(Indicadores!$F12:$Q12,Config!$B$7-1)="","",INDEX(Indicadores!$F12:$Q12,Config!$B$7-1)))</f>
-        <v/>
+        <v>2.6</v>
       </c>
       <c r="D12" s="10">
         <f>IF(OR(B12="",C12="",C12=0),"",(B12-C12)/ABS(C12))</f>
-        <v/>
+        <v>-0.076923076923077</v>
       </c>
       <c r="E12" s="9">
         <f>IF(OR(Indicadores!A12="",Indicadores!D12=""),"",Indicadores!D12)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="F12" s="10">
         <f>IF(OR(B12="",E12="",E12=0),"",(B12-E12)/ABS(E12))</f>
-        <v/>
-      </c>
-      <c r="G12" s="11">
+        <v>-0.2</v>
+      </c>
+      <c r="G12" s="11" t="str">
         <f>IF(OR(B12="",E12=""),"",IF(Indicadores!E12="Não",IF(B12&lt;=E12,"No alvo","Acima da meta"),IF(B12&gt;=E12,"No alvo","Abaixo da meta")))</f>
-        <v/>
+        <v>No alvo</v>
       </c>
       <c r="H12" s="9">
         <f>IF(Indicadores!A12="","",Indicadores!R12)</f>
-        <v/>
-      </c>
-      <c r="I12" s="11">
+        <v>3.22222222222222</v>
+      </c>
+      <c r="I12" s="11" t="str">
         <f>IF(Indicadores!A12="","",Indicadores!B12)</f>
-        <v/>
+        <v>%</v>
       </c>
       <c r="N12" s="12">
         <f>IF(Indicadores!C12="",2,Indicadores!C12)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="O12" s="12">
         <f>IF(OR(F12="",G12="",G12="No alvo"),"",IF(Indicadores!E12="Não",F12,-F12))</f>
@@ -1381,45 +1381,45 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8">
+      <c r="A13" s="8" t="str">
         <f>IF(Indicadores!A13="","",Indicadores!A13)</f>
-        <v/>
+        <v>Atendimentos realizados</v>
       </c>
       <c r="B13" s="9">
         <f>IF(Indicadores!A13="","",IF(INDEX(Indicadores!$F13:$Q13,Config!$B$7)="","",INDEX(Indicadores!$F13:$Q13,Config!$B$7)))</f>
-        <v/>
+        <v>63</v>
       </c>
       <c r="C13" s="9">
         <f>IF(OR(Indicadores!A13="",Config!$B$7=1),"",IF(INDEX(Indicadores!$F13:$Q13,Config!$B$7-1)="","",INDEX(Indicadores!$F13:$Q13,Config!$B$7-1)))</f>
-        <v/>
+        <v>66</v>
       </c>
       <c r="D13" s="10">
         <f>IF(OR(B13="",C13="",C13=0),"",(B13-C13)/ABS(C13))</f>
-        <v/>
+        <v>-0.0454545454545455</v>
       </c>
       <c r="E13" s="9">
         <f>IF(OR(Indicadores!A13="",Indicadores!D13=""),"",Indicadores!D13)</f>
-        <v/>
+        <v>60</v>
       </c>
       <c r="F13" s="10">
         <f>IF(OR(B13="",E13="",E13=0),"",(B13-E13)/ABS(E13))</f>
-        <v/>
-      </c>
-      <c r="G13" s="11">
+        <v>0.05</v>
+      </c>
+      <c r="G13" s="11" t="str">
         <f>IF(OR(B13="",E13=""),"",IF(Indicadores!E13="Não",IF(B13&lt;=E13,"No alvo","Acima da meta"),IF(B13&gt;=E13,"No alvo","Abaixo da meta")))</f>
-        <v/>
+        <v>No alvo</v>
       </c>
       <c r="H13" s="9">
         <f>IF(Indicadores!A13="","",Indicadores!R13)</f>
-        <v/>
-      </c>
-      <c r="I13" s="11">
+        <v>536</v>
+      </c>
+      <c r="I13" s="11" t="str">
         <f>IF(Indicadores!A13="","",Indicadores!B13)</f>
-        <v/>
+        <v>un</v>
       </c>
       <c r="N13" s="12">
         <f>IF(Indicadores!C13="",2,Indicadores!C13)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O13" s="12">
         <f>IF(OR(F13="",G13="",G13="No alvo"),"",IF(Indicadores!E13="Não",F13,-F13))</f>
@@ -1427,45 +1427,45 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8">
+      <c r="A14" s="8" t="str">
         <f>IF(Indicadores!A14="","",Indicadores!A14)</f>
-        <v/>
+        <v>NPS</v>
       </c>
       <c r="B14" s="9">
         <f>IF(Indicadores!A14="","",IF(INDEX(Indicadores!$F14:$Q14,Config!$B$7)="","",INDEX(Indicadores!$F14:$Q14,Config!$B$7)))</f>
-        <v/>
+        <v>72</v>
       </c>
       <c r="C14" s="9">
         <f>IF(OR(Indicadores!A14="",Config!$B$7=1),"",IF(INDEX(Indicadores!$F14:$Q14,Config!$B$7-1)="","",INDEX(Indicadores!$F14:$Q14,Config!$B$7-1)))</f>
-        <v/>
+        <v>73</v>
       </c>
       <c r="D14" s="10">
         <f>IF(OR(B14="",C14="",C14=0),"",(B14-C14)/ABS(C14))</f>
-        <v/>
+        <v>-0.0136986301369863</v>
       </c>
       <c r="E14" s="9">
         <f>IF(OR(Indicadores!A14="",Indicadores!D14=""),"",Indicadores!D14)</f>
-        <v/>
+        <v>70</v>
       </c>
       <c r="F14" s="10">
         <f>IF(OR(B14="",E14="",E14=0),"",(B14-E14)/ABS(E14))</f>
-        <v/>
-      </c>
-      <c r="G14" s="11">
+        <v>0.0285714285714286</v>
+      </c>
+      <c r="G14" s="11" t="str">
         <f>IF(OR(B14="",E14=""),"",IF(Indicadores!E14="Não",IF(B14&lt;=E14,"No alvo","Acima da meta"),IF(B14&gt;=E14,"No alvo","Abaixo da meta")))</f>
-        <v/>
+        <v>No alvo</v>
       </c>
       <c r="H14" s="9">
         <f>IF(Indicadores!A14="","",Indicadores!R14)</f>
-        <v/>
-      </c>
-      <c r="I14" s="11">
+        <v>68.8888888888889</v>
+      </c>
+      <c r="I14" s="11" t="str">
         <f>IF(Indicadores!A14="","",Indicadores!B14)</f>
-        <v/>
+        <v>pts</v>
       </c>
       <c r="N14" s="12">
         <f>IF(Indicadores!C14="",2,Indicadores!C14)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O14" s="12">
         <f>IF(OR(F14="",G14="",G14="No alvo"),"",IF(Indicadores!E14="Não",F14,-F14))</f>
@@ -1473,45 +1473,45 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8">
+      <c r="A15" s="8" t="str">
         <f>IF(Indicadores!A15="","",Indicadores!A15)</f>
-        <v/>
+        <v>Horas extras da equipe</v>
       </c>
       <c r="B15" s="9">
         <f>IF(Indicadores!A15="","",IF(INDEX(Indicadores!$F15:$Q15,Config!$B$7)="","",INDEX(Indicadores!$F15:$Q15,Config!$B$7)))</f>
-        <v/>
+        <v>12</v>
       </c>
       <c r="C15" s="9">
         <f>IF(OR(Indicadores!A15="",Config!$B$7=1),"",IF(INDEX(Indicadores!$F15:$Q15,Config!$B$7-1)="","",INDEX(Indicadores!$F15:$Q15,Config!$B$7-1)))</f>
-        <v/>
+        <v>14</v>
       </c>
       <c r="D15" s="10">
         <f>IF(OR(B15="",C15="",C15=0),"",(B15-C15)/ABS(C15))</f>
-        <v/>
+        <v>-0.142857142857143</v>
       </c>
       <c r="E15" s="9">
         <f>IF(OR(Indicadores!A15="",Indicadores!D15=""),"",Indicadores!D15)</f>
-        <v/>
+        <v>20</v>
       </c>
       <c r="F15" s="10">
         <f>IF(OR(B15="",E15="",E15=0),"",(B15-E15)/ABS(E15))</f>
-        <v/>
-      </c>
-      <c r="G15" s="11">
+        <v>-0.4</v>
+      </c>
+      <c r="G15" s="11" t="str">
         <f>IF(OR(B15="",E15=""),"",IF(Indicadores!E15="Não",IF(B15&lt;=E15,"No alvo","Acima da meta"),IF(B15&gt;=E15,"No alvo","Abaixo da meta")))</f>
-        <v/>
+        <v>No alvo</v>
       </c>
       <c r="H15" s="9">
         <f>IF(Indicadores!A15="","",Indicadores!R15)</f>
-        <v/>
-      </c>
-      <c r="I15" s="11">
+        <v>173</v>
+      </c>
+      <c r="I15" s="11" t="str">
         <f>IF(Indicadores!A15="","",Indicadores!B15)</f>
-        <v/>
+        <v>h</v>
       </c>
       <c r="N15" s="12">
         <f>IF(Indicadores!C15="",2,Indicadores!C15)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O15" s="12">
         <f>IF(OR(F15="",G15="",G15="No alvo"),"",IF(Indicadores!E15="Não",F15,-F15))</f>
@@ -1519,45 +1519,45 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="8">
+      <c r="A16" s="8" t="str">
         <f>IF(Indicadores!A16="","",Indicadores!A16)</f>
-        <v/>
+        <v>Custo por lead</v>
       </c>
       <c r="B16" s="9">
         <f>IF(Indicadores!A16="","",IF(INDEX(Indicadores!$F16:$Q16,Config!$B$7)="","",INDEX(Indicadores!$F16:$Q16,Config!$B$7)))</f>
-        <v/>
+        <v>40.7</v>
       </c>
       <c r="C16" s="9">
         <f>IF(OR(Indicadores!A16="",Config!$B$7=1),"",IF(INDEX(Indicadores!$F16:$Q16,Config!$B$7-1)="","",INDEX(Indicadores!$F16:$Q16,Config!$B$7-1)))</f>
-        <v/>
+        <v>39.5</v>
       </c>
       <c r="D16" s="10">
         <f>IF(OR(B16="",C16="",C16=0),"",(B16-C16)/ABS(C16))</f>
-        <v/>
+        <v>0.0303797468354431</v>
       </c>
       <c r="E16" s="9">
         <f>IF(OR(Indicadores!A16="",Indicadores!D16=""),"",Indicadores!D16)</f>
-        <v/>
+        <v>45</v>
       </c>
       <c r="F16" s="10">
         <f>IF(OR(B16="",E16="",E16=0),"",(B16-E16)/ABS(E16))</f>
-        <v/>
-      </c>
-      <c r="G16" s="11">
+        <v>-0.0955555555555555</v>
+      </c>
+      <c r="G16" s="11" t="str">
         <f>IF(OR(B16="",E16=""),"",IF(Indicadores!E16="Não",IF(B16&lt;=E16,"No alvo","Acima da meta"),IF(B16&gt;=E16,"No alvo","Abaixo da meta")))</f>
-        <v/>
+        <v>No alvo</v>
       </c>
       <c r="H16" s="9">
         <f>IF(Indicadores!A16="","",Indicadores!R16)</f>
-        <v/>
-      </c>
-      <c r="I16" s="11">
+        <v>405.8</v>
+      </c>
+      <c r="I16" s="11" t="str">
         <f>IF(Indicadores!A16="","",Indicadores!B16)</f>
-        <v/>
+        <v>R$</v>
       </c>
       <c r="N16" s="12">
         <f>IF(Indicadores!C16="",2,Indicadores!C16)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="O16" s="12">
         <f>IF(OR(F16="",G16="",G16="No alvo"),"",IF(Indicadores!E16="Não",F16,-F16))</f>
@@ -1570,9 +1570,9 @@
           <t>Indicador do gráfico</t>
         </is>
       </c>
-      <c r="B18" s="14">
+      <c r="B18" s="14" t="str">
         <f>Indicadores!A5</f>
-        <v/>
+        <v>Receita</v>
       </c>
       <c r="C18" s="15" t="n"/>
       <c r="D18" s="16" t="n"/>
@@ -1666,51 +1666,51 @@
       </c>
       <c r="B39" s="18">
         <f>IFERROR(IF(INDEX(Indicadores!$F$5:$Q$16,MATCH($B$18,Indicadores!$A$5:$A$16,0),1)="",NA(),INDEX(Indicadores!$F$5:$Q$16,MATCH($B$18,Indicadores!$A$5:$A$16,0),1)),NA())</f>
-        <v/>
+        <v>98500</v>
       </c>
       <c r="C39" s="18">
         <f>IFERROR(IF(INDEX(Indicadores!$F$5:$Q$16,MATCH($B$18,Indicadores!$A$5:$A$16,0),2)="",NA(),INDEX(Indicadores!$F$5:$Q$16,MATCH($B$18,Indicadores!$A$5:$A$16,0),2)),NA())</f>
-        <v/>
+        <v>101200</v>
       </c>
       <c r="D39" s="18">
         <f>IFERROR(IF(INDEX(Indicadores!$F$5:$Q$16,MATCH($B$18,Indicadores!$A$5:$A$16,0),3)="",NA(),INDEX(Indicadores!$F$5:$Q$16,MATCH($B$18,Indicadores!$A$5:$A$16,0),3)),NA())</f>
-        <v/>
+        <v>112400</v>
       </c>
       <c r="E39" s="18">
         <f>IFERROR(IF(INDEX(Indicadores!$F$5:$Q$16,MATCH($B$18,Indicadores!$A$5:$A$16,0),4)="",NA(),INDEX(Indicadores!$F$5:$Q$16,MATCH($B$18,Indicadores!$A$5:$A$16,0),4)),NA())</f>
-        <v/>
+        <v>109800</v>
       </c>
       <c r="F39" s="18">
         <f>IFERROR(IF(INDEX(Indicadores!$F$5:$Q$16,MATCH($B$18,Indicadores!$A$5:$A$16,0),5)="",NA(),INDEX(Indicadores!$F$5:$Q$16,MATCH($B$18,Indicadores!$A$5:$A$16,0),5)),NA())</f>
-        <v/>
+        <v>118300</v>
       </c>
       <c r="G39" s="18">
         <f>IFERROR(IF(INDEX(Indicadores!$F$5:$Q$16,MATCH($B$18,Indicadores!$A$5:$A$16,0),6)="",NA(),INDEX(Indicadores!$F$5:$Q$16,MATCH($B$18,Indicadores!$A$5:$A$16,0),6)),NA())</f>
-        <v/>
+        <v>121900</v>
       </c>
       <c r="H39" s="18">
         <f>IFERROR(IF(INDEX(Indicadores!$F$5:$Q$16,MATCH($B$18,Indicadores!$A$5:$A$16,0),7)="",NA(),INDEX(Indicadores!$F$5:$Q$16,MATCH($B$18,Indicadores!$A$5:$A$16,0),7)),NA())</f>
-        <v/>
+        <v>115700</v>
       </c>
       <c r="I39" s="18">
         <f>IFERROR(IF(INDEX(Indicadores!$F$5:$Q$16,MATCH($B$18,Indicadores!$A$5:$A$16,0),8)="",NA(),INDEX(Indicadores!$F$5:$Q$16,MATCH($B$18,Indicadores!$A$5:$A$16,0),8)),NA())</f>
-        <v/>
+        <v>124600</v>
       </c>
       <c r="J39" s="18">
         <f>IFERROR(IF(INDEX(Indicadores!$F$5:$Q$16,MATCH($B$18,Indicadores!$A$5:$A$16,0),9)="",NA(),INDEX(Indicadores!$F$5:$Q$16,MATCH($B$18,Indicadores!$A$5:$A$16,0),9)),NA())</f>
-        <v/>
-      </c>
-      <c r="K39" s="18">
+        <v>131200</v>
+      </c>
+      <c r="K39" s="18" t="e">
         <f>IFERROR(IF(INDEX(Indicadores!$F$5:$Q$16,MATCH($B$18,Indicadores!$A$5:$A$16,0),10)="",NA(),INDEX(Indicadores!$F$5:$Q$16,MATCH($B$18,Indicadores!$A$5:$A$16,0),10)),NA())</f>
-        <v/>
-      </c>
-      <c r="L39" s="18">
+        <v>#N/A</v>
+      </c>
+      <c r="L39" s="18" t="e">
         <f>IFERROR(IF(INDEX(Indicadores!$F$5:$Q$16,MATCH($B$18,Indicadores!$A$5:$A$16,0),11)="",NA(),INDEX(Indicadores!$F$5:$Q$16,MATCH($B$18,Indicadores!$A$5:$A$16,0),11)),NA())</f>
-        <v/>
-      </c>
-      <c r="M39" s="18">
+        <v>#N/A</v>
+      </c>
+      <c r="M39" s="18" t="e">
         <f>IFERROR(IF(INDEX(Indicadores!$F$5:$Q$16,MATCH($B$18,Indicadores!$A$5:$A$16,0),12)="",NA(),INDEX(Indicadores!$F$5:$Q$16,MATCH($B$18,Indicadores!$A$5:$A$16,0),12)),NA())</f>
-        <v/>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="40">
@@ -1721,51 +1721,51 @@
       </c>
       <c r="B40" s="18">
         <f>IFERROR(INDEX(Indicadores!$D$5:$D$16,MATCH($B$18,Indicadores!$A$5:$A$16,0)),NA())</f>
-        <v/>
+        <v>120000</v>
       </c>
       <c r="C40" s="18">
         <f>IFERROR(INDEX(Indicadores!$D$5:$D$16,MATCH($B$18,Indicadores!$A$5:$A$16,0)),NA())</f>
-        <v/>
+        <v>120000</v>
       </c>
       <c r="D40" s="18">
         <f>IFERROR(INDEX(Indicadores!$D$5:$D$16,MATCH($B$18,Indicadores!$A$5:$A$16,0)),NA())</f>
-        <v/>
+        <v>120000</v>
       </c>
       <c r="E40" s="18">
         <f>IFERROR(INDEX(Indicadores!$D$5:$D$16,MATCH($B$18,Indicadores!$A$5:$A$16,0)),NA())</f>
-        <v/>
+        <v>120000</v>
       </c>
       <c r="F40" s="18">
         <f>IFERROR(INDEX(Indicadores!$D$5:$D$16,MATCH($B$18,Indicadores!$A$5:$A$16,0)),NA())</f>
-        <v/>
+        <v>120000</v>
       </c>
       <c r="G40" s="18">
         <f>IFERROR(INDEX(Indicadores!$D$5:$D$16,MATCH($B$18,Indicadores!$A$5:$A$16,0)),NA())</f>
-        <v/>
+        <v>120000</v>
       </c>
       <c r="H40" s="18">
         <f>IFERROR(INDEX(Indicadores!$D$5:$D$16,MATCH($B$18,Indicadores!$A$5:$A$16,0)),NA())</f>
-        <v/>
+        <v>120000</v>
       </c>
       <c r="I40" s="18">
         <f>IFERROR(INDEX(Indicadores!$D$5:$D$16,MATCH($B$18,Indicadores!$A$5:$A$16,0)),NA())</f>
-        <v/>
+        <v>120000</v>
       </c>
       <c r="J40" s="18">
         <f>IFERROR(INDEX(Indicadores!$D$5:$D$16,MATCH($B$18,Indicadores!$A$5:$A$16,0)),NA())</f>
-        <v/>
+        <v>120000</v>
       </c>
       <c r="K40" s="18">
         <f>IFERROR(INDEX(Indicadores!$D$5:$D$16,MATCH($B$18,Indicadores!$A$5:$A$16,0)),NA())</f>
-        <v/>
+        <v>120000</v>
       </c>
       <c r="L40" s="18">
         <f>IFERROR(INDEX(Indicadores!$D$5:$D$16,MATCH($B$18,Indicadores!$A$5:$A$16,0)),NA())</f>
-        <v/>
+        <v>120000</v>
       </c>
       <c r="M40" s="18">
         <f>IFERROR(INDEX(Indicadores!$D$5:$D$16,MATCH($B$18,Indicadores!$A$5:$A$16,0)),NA())</f>
-        <v/>
+        <v>120000</v>
       </c>
     </row>
   </sheetData>
@@ -1831,81 +1831,81 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13">
+      <c r="A4" s="13" t="str">
         <f>"Relatório de "&amp;Config!B6&amp;" de "&amp;Config!B5&amp;" · "&amp;Config!B4</f>
-        <v/>
+        <v>Relatório de Setembro de 2026 · Prisma Comunicação (exemplo fictício)</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="19">
+      <c r="A6" s="19" t="str">
         <f>IF(OR(Indicadores!A5="",Painel!B5=""),"","• "&amp;Indicadores!A5&amp;": "&amp;IF(Indicadores!B5="R$","R$ ","")&amp;FIXED(Painel!B5,IF(Indicadores!C5="",0,Indicadores!C5))&amp;IF(OR(Indicadores!B5="R$",Indicadores!B5=""),""," "&amp;Indicadores!B5)&amp;IF(Painel!C5&lt;&gt;"",IF(Painel!D5&gt;=0," (+"," (")&amp;FIXED(Painel!D5*100,0)&amp;"% em relação a "&amp;Config!$B$8&amp;")","")&amp;IF(Painel!E5&lt;&gt;"","; meta "&amp;IF(Indicadores!B5="R$","R$ ","")&amp;FIXED(Painel!E5,IF(Indicadores!C5="",0,Indicadores!C5))&amp;IF(OR(Indicadores!B5="R$",Indicadores!B5=""),""," "&amp;Indicadores!B5)&amp;", "&amp;LOWER(Painel!G5),"")&amp;".")</f>
-        <v/>
+        <v>• Receita: R$ 131.200 (+5% em relação a Agosto); meta R$ 120.000, no alvo.</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="19">
+      <c r="A7" s="19" t="str">
         <f>IF(OR(Indicadores!A6="",Painel!B6=""),"","• "&amp;Indicadores!A6&amp;": "&amp;IF(Indicadores!B6="R$","R$ ","")&amp;FIXED(Painel!B6,IF(Indicadores!C6="",0,Indicadores!C6))&amp;IF(OR(Indicadores!B6="R$",Indicadores!B6=""),""," "&amp;Indicadores!B6)&amp;IF(Painel!C6&lt;&gt;"",IF(Painel!D6&gt;=0," (+"," (")&amp;FIXED(Painel!D6*100,0)&amp;"% em relação a "&amp;Config!$B$8&amp;")","")&amp;IF(Painel!E6&lt;&gt;"","; meta "&amp;IF(Indicadores!B6="R$","R$ ","")&amp;FIXED(Painel!E6,IF(Indicadores!C6="",0,Indicadores!C6))&amp;IF(OR(Indicadores!B6="R$",Indicadores!B6=""),""," "&amp;Indicadores!B6)&amp;", "&amp;LOWER(Painel!G6),"")&amp;".")</f>
-        <v/>
+        <v>• Despesas: R$ 89.800 (+3% em relação a Agosto); meta R$ 85.000, acima da meta.</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="19">
+      <c r="A8" s="19" t="str">
         <f>IF(OR(Indicadores!A7="",Painel!B7=""),"","• "&amp;Indicadores!A7&amp;": "&amp;IF(Indicadores!B7="R$","R$ ","")&amp;FIXED(Painel!B7,IF(Indicadores!C7="",0,Indicadores!C7))&amp;IF(OR(Indicadores!B7="R$",Indicadores!B7=""),""," "&amp;Indicadores!B7)&amp;IF(Painel!C7&lt;&gt;"",IF(Painel!D7&gt;=0," (+"," (")&amp;FIXED(Painel!D7*100,0)&amp;"% em relação a "&amp;Config!$B$8&amp;")","")&amp;IF(Painel!E7&lt;&gt;"","; meta "&amp;IF(Indicadores!B7="R$","R$ ","")&amp;FIXED(Painel!E7,IF(Indicadores!C7="",0,Indicadores!C7))&amp;IF(OR(Indicadores!B7="R$",Indicadores!B7=""),""," "&amp;Indicadores!B7)&amp;", "&amp;LOWER(Painel!G7),"")&amp;".")</f>
-        <v/>
+        <v>• Resultado (receita - despesas): R$ 41.400 (+11% em relação a Agosto); meta R$ 35.000, no alvo.</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="19">
+      <c r="A9" s="19" t="str">
         <f>IF(OR(Indicadores!A8="",Painel!B8=""),"","• "&amp;Indicadores!A8&amp;": "&amp;IF(Indicadores!B8="R$","R$ ","")&amp;FIXED(Painel!B8,IF(Indicadores!C8="",0,Indicadores!C8))&amp;IF(OR(Indicadores!B8="R$",Indicadores!B8=""),""," "&amp;Indicadores!B8)&amp;IF(Painel!C8&lt;&gt;"",IF(Painel!D8&gt;=0," (+"," (")&amp;FIXED(Painel!D8*100,0)&amp;"% em relação a "&amp;Config!$B$8&amp;")","")&amp;IF(Painel!E8&lt;&gt;"","; meta "&amp;IF(Indicadores!B8="R$","R$ ","")&amp;FIXED(Painel!E8,IF(Indicadores!C8="",0,Indicadores!C8))&amp;IF(OR(Indicadores!B8="R$",Indicadores!B8=""),""," "&amp;Indicadores!B8)&amp;", "&amp;LOWER(Painel!G8),"")&amp;".")</f>
-        <v/>
+        <v>• Novos clientes: 6 un (-14% em relação a Agosto); meta 6 un, no alvo.</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="19">
+      <c r="A10" s="19" t="str">
         <f>IF(OR(Indicadores!A9="",Painel!B9=""),"","• "&amp;Indicadores!A9&amp;": "&amp;IF(Indicadores!B9="R$","R$ ","")&amp;FIXED(Painel!B9,IF(Indicadores!C9="",0,Indicadores!C9))&amp;IF(OR(Indicadores!B9="R$",Indicadores!B9=""),""," "&amp;Indicadores!B9)&amp;IF(Painel!C9&lt;&gt;"",IF(Painel!D9&gt;=0," (+"," (")&amp;FIXED(Painel!D9*100,0)&amp;"% em relação a "&amp;Config!$B$8&amp;")","")&amp;IF(Painel!E9&lt;&gt;"","; meta "&amp;IF(Indicadores!B9="R$","R$ ","")&amp;FIXED(Painel!E9,IF(Indicadores!C9="",0,Indicadores!C9))&amp;IF(OR(Indicadores!B9="R$",Indicadores!B9=""),""," "&amp;Indicadores!B9)&amp;", "&amp;LOWER(Painel!G9),"")&amp;".")</f>
-        <v/>
+        <v>• Leads recebidos: 137 un (-4% em relação a Agosto); meta 120 un, no alvo.</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="19">
+      <c r="A11" s="19" t="str">
         <f>IF(OR(Indicadores!A10="",Painel!B10=""),"","• "&amp;Indicadores!A10&amp;": "&amp;IF(Indicadores!B10="R$","R$ ","")&amp;FIXED(Painel!B10,IF(Indicadores!C10="",0,Indicadores!C10))&amp;IF(OR(Indicadores!B10="R$",Indicadores!B10=""),""," "&amp;Indicadores!B10)&amp;IF(Painel!C10&lt;&gt;"",IF(Painel!D10&gt;=0," (+"," (")&amp;FIXED(Painel!D10*100,0)&amp;"% em relação a "&amp;Config!$B$8&amp;")","")&amp;IF(Painel!E10&lt;&gt;"","; meta "&amp;IF(Indicadores!B10="R$","R$ ","")&amp;FIXED(Painel!E10,IF(Indicadores!C10="",0,Indicadores!C10))&amp;IF(OR(Indicadores!B10="R$",Indicadores!B10=""),""," "&amp;Indicadores!B10)&amp;", "&amp;LOWER(Painel!G10),"")&amp;".")</f>
-        <v/>
+        <v>• Taxa de conversão de leads: 4,4 % (-10% em relação a Agosto); meta 5,0 %, abaixo da meta.</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="19">
+      <c r="A12" s="19" t="str">
         <f>IF(OR(Indicadores!A11="",Painel!B11=""),"","• "&amp;Indicadores!A11&amp;": "&amp;IF(Indicadores!B11="R$","R$ ","")&amp;FIXED(Painel!B11,IF(Indicadores!C11="",0,Indicadores!C11))&amp;IF(OR(Indicadores!B11="R$",Indicadores!B11=""),""," "&amp;Indicadores!B11)&amp;IF(Painel!C11&lt;&gt;"",IF(Painel!D11&gt;=0," (+"," (")&amp;FIXED(Painel!D11*100,0)&amp;"% em relação a "&amp;Config!$B$8&amp;")","")&amp;IF(Painel!E11&lt;&gt;"","; meta "&amp;IF(Indicadores!B11="R$","R$ ","")&amp;FIXED(Painel!E11,IF(Indicadores!C11="",0,Indicadores!C11))&amp;IF(OR(Indicadores!B11="R$",Indicadores!B11=""),""," "&amp;Indicadores!B11)&amp;", "&amp;LOWER(Painel!G11),"")&amp;".")</f>
-        <v/>
+        <v>• Ticket médio: R$ 9.700 (+3% em relação a Agosto); meta R$ 9.000, no alvo.</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="19">
+      <c r="A13" s="19" t="str">
         <f>IF(OR(Indicadores!A12="",Painel!B12=""),"","• "&amp;Indicadores!A12&amp;": "&amp;IF(Indicadores!B12="R$","R$ ","")&amp;FIXED(Painel!B12,IF(Indicadores!C12="",0,Indicadores!C12))&amp;IF(OR(Indicadores!B12="R$",Indicadores!B12=""),""," "&amp;Indicadores!B12)&amp;IF(Painel!C12&lt;&gt;"",IF(Painel!D12&gt;=0," (+"," (")&amp;FIXED(Painel!D12*100,0)&amp;"% em relação a "&amp;Config!$B$8&amp;")","")&amp;IF(Painel!E12&lt;&gt;"","; meta "&amp;IF(Indicadores!B12="R$","R$ ","")&amp;FIXED(Painel!E12,IF(Indicadores!C12="",0,Indicadores!C12))&amp;IF(OR(Indicadores!B12="R$",Indicadores!B12=""),""," "&amp;Indicadores!B12)&amp;", "&amp;LOWER(Painel!G12),"")&amp;".")</f>
-        <v/>
+        <v>• Inadimplência: 2,4 % (-8% em relação a Agosto); meta 3,0 %, no alvo.</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="19">
+      <c r="A14" s="19" t="str">
         <f>IF(OR(Indicadores!A13="",Painel!B13=""),"","• "&amp;Indicadores!A13&amp;": "&amp;IF(Indicadores!B13="R$","R$ ","")&amp;FIXED(Painel!B13,IF(Indicadores!C13="",0,Indicadores!C13))&amp;IF(OR(Indicadores!B13="R$",Indicadores!B13=""),""," "&amp;Indicadores!B13)&amp;IF(Painel!C13&lt;&gt;"",IF(Painel!D13&gt;=0," (+"," (")&amp;FIXED(Painel!D13*100,0)&amp;"% em relação a "&amp;Config!$B$8&amp;")","")&amp;IF(Painel!E13&lt;&gt;"","; meta "&amp;IF(Indicadores!B13="R$","R$ ","")&amp;FIXED(Painel!E13,IF(Indicadores!C13="",0,Indicadores!C13))&amp;IF(OR(Indicadores!B13="R$",Indicadores!B13=""),""," "&amp;Indicadores!B13)&amp;", "&amp;LOWER(Painel!G13),"")&amp;".")</f>
-        <v/>
+        <v>• Atendimentos realizados: 63 un (-5% em relação a Agosto); meta 60 un, no alvo.</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="19">
+      <c r="A15" s="19" t="str">
         <f>IF(OR(Indicadores!A14="",Painel!B14=""),"","• "&amp;Indicadores!A14&amp;": "&amp;IF(Indicadores!B14="R$","R$ ","")&amp;FIXED(Painel!B14,IF(Indicadores!C14="",0,Indicadores!C14))&amp;IF(OR(Indicadores!B14="R$",Indicadores!B14=""),""," "&amp;Indicadores!B14)&amp;IF(Painel!C14&lt;&gt;"",IF(Painel!D14&gt;=0," (+"," (")&amp;FIXED(Painel!D14*100,0)&amp;"% em relação a "&amp;Config!$B$8&amp;")","")&amp;IF(Painel!E14&lt;&gt;"","; meta "&amp;IF(Indicadores!B14="R$","R$ ","")&amp;FIXED(Painel!E14,IF(Indicadores!C14="",0,Indicadores!C14))&amp;IF(OR(Indicadores!B14="R$",Indicadores!B14=""),""," "&amp;Indicadores!B14)&amp;", "&amp;LOWER(Painel!G14),"")&amp;".")</f>
-        <v/>
+        <v>• NPS: 72 pts (-1% em relação a Agosto); meta 70 pts, no alvo.</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="19">
+      <c r="A16" s="19" t="str">
         <f>IF(OR(Indicadores!A15="",Painel!B15=""),"","• "&amp;Indicadores!A15&amp;": "&amp;IF(Indicadores!B15="R$","R$ ","")&amp;FIXED(Painel!B15,IF(Indicadores!C15="",0,Indicadores!C15))&amp;IF(OR(Indicadores!B15="R$",Indicadores!B15=""),""," "&amp;Indicadores!B15)&amp;IF(Painel!C15&lt;&gt;"",IF(Painel!D15&gt;=0," (+"," (")&amp;FIXED(Painel!D15*100,0)&amp;"% em relação a "&amp;Config!$B$8&amp;")","")&amp;IF(Painel!E15&lt;&gt;"","; meta "&amp;IF(Indicadores!B15="R$","R$ ","")&amp;FIXED(Painel!E15,IF(Indicadores!C15="",0,Indicadores!C15))&amp;IF(OR(Indicadores!B15="R$",Indicadores!B15=""),""," "&amp;Indicadores!B15)&amp;", "&amp;LOWER(Painel!G15),"")&amp;".")</f>
-        <v/>
+        <v>• Horas extras da equipe: 12 h (-14% em relação a Agosto); meta 20 h, no alvo.</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="19">
+      <c r="A17" s="19" t="str">
         <f>IF(OR(Indicadores!A16="",Painel!B16=""),"","• "&amp;Indicadores!A16&amp;": "&amp;IF(Indicadores!B16="R$","R$ ","")&amp;FIXED(Painel!B16,IF(Indicadores!C16="",0,Indicadores!C16))&amp;IF(OR(Indicadores!B16="R$",Indicadores!B16=""),""," "&amp;Indicadores!B16)&amp;IF(Painel!C16&lt;&gt;"",IF(Painel!D16&gt;=0," (+"," (")&amp;FIXED(Painel!D16*100,0)&amp;"% em relação a "&amp;Config!$B$8&amp;")","")&amp;IF(Painel!E16&lt;&gt;"","; meta "&amp;IF(Indicadores!B16="R$","R$ ","")&amp;FIXED(Painel!E16,IF(Indicadores!C16="",0,Indicadores!C16))&amp;IF(OR(Indicadores!B16="R$",Indicadores!B16=""),""," "&amp;Indicadores!B16)&amp;", "&amp;LOWER(Painel!G16),"")&amp;".")</f>
-        <v/>
+        <v>• Custo por lead: R$ 40,70 (+3% em relação a Agosto); meta R$ 45,00, no alvo.</v>
       </c>
     </row>
     <row r="19">
@@ -1916,27 +1916,27 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="19">
+      <c r="A20" s="19" t="str">
         <f>IFERROR("• Maior alta contra o mês anterior: "&amp;INDEX(Painel!$A$5:$A$16,MATCH(MAX(Painel!$D$5:$D$16),Painel!$D$5:$D$16,0))&amp;" ("&amp;IF(MAX(Painel!$D$5:$D$16)&gt;=0,"+","")&amp;FIXED(MAX(Painel!$D$5:$D$16)*100,0)&amp;"%).","• Maior alta: preencha ao menos dois meses.")</f>
-        <v/>
+        <v>• Maior alta contra o mês anterior: Resultado (receita - despesas) (+11%).</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="19">
+      <c r="A21" s="19" t="str">
         <f>IFERROR("• Maior queda contra o mês anterior: "&amp;INDEX(Painel!$A$5:$A$16,MATCH(MIN(Painel!$D$5:$D$16),Painel!$D$5:$D$16,0))&amp;" ("&amp;FIXED(MIN(Painel!$D$5:$D$16)*100,0)&amp;"%).","")</f>
-        <v/>
+        <v>• Maior queda contra o mês anterior: Novos clientes (-14%).</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="19">
+      <c r="A22" s="19" t="str">
         <f>IF(COUNT(Painel!$O$5:$O$16)=0,"• Nenhum indicador fora da meta.",IFERROR("• Mais longe da meta: "&amp;INDEX(Painel!$A$5:$A$16,MATCH(MAX(Painel!$O$5:$O$16),Painel!$O$5:$O$16,0))&amp;" ("&amp;IF(INDEX(Painel!$F$5:$F$16,MATCH(MAX(Painel!$O$5:$O$16),Painel!$O$5:$O$16,0))&gt;=0,"+","")&amp;FIXED(INDEX(Painel!$F$5:$F$16,MATCH(MAX(Painel!$O$5:$O$16),Painel!$O$5:$O$16,0))*100,0)&amp;"% da meta, "&amp;LOWER(INDEX(Painel!$G$5:$G$16,MATCH(MAX(Painel!$O$5:$O$16),Painel!$O$5:$O$16,0)))&amp;").",""))</f>
-        <v/>
+        <v>• Mais longe da meta: Taxa de conversão de leads (-12% da meta, abaixo da meta).</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="19">
+      <c r="A23" s="19" t="str">
         <f>IFERROR("• Indicadores no alvo: "&amp;COUNTIF(Painel!$G$5:$G$16,"No alvo")&amp;" de "&amp;COUNTIF(Painel!$G$5:$G$16,"&lt;&gt;")&amp;".","")</f>
-        <v/>
+        <v>• Indicadores no alvo: 10 de 12.</v>
       </c>
     </row>
     <row r="25">
@@ -1947,9 +1947,25 @@
       </c>
     </row>
     <row r="26" ht="300" customHeight="1">
-      <c r="A26" s="20">
+      <c r="A26" s="20" t="str">
         <f>A4&amp;CHAR(10)&amp;IF(A6="","",A6&amp;CHAR(10)) &amp; IF(A7="","",A7&amp;CHAR(10)) &amp; IF(A8="","",A8&amp;CHAR(10)) &amp; IF(A9="","",A9&amp;CHAR(10)) &amp; IF(A10="","",A10&amp;CHAR(10)) &amp; IF(A11="","",A11&amp;CHAR(10)) &amp; IF(A12="","",A12&amp;CHAR(10)) &amp; IF(A13="","",A13&amp;CHAR(10)) &amp; IF(A14="","",A14&amp;CHAR(10)) &amp; IF(A15="","",A15&amp;CHAR(10)) &amp; IF(A16="","",A16&amp;CHAR(10)) &amp; IF(A17="","",A17&amp;CHAR(10))&amp;CHAR(10)&amp;A20&amp;CHAR(10)&amp;A21&amp;CHAR(10)&amp;A22&amp;CHAR(10)&amp;A23</f>
-        <v/>
+        <v>Relatório de Setembro de 2026 · Prisma Comunicação (exemplo fictício)
+• Receita: R$ 131.200 (+5% em relação a Agosto); meta R$ 120.000, no alvo.
+• Despesas: R$ 89.800 (+3% em relação a Agosto); meta R$ 85.000, acima da meta.
+• Resultado (receita - despesas): R$ 41.400 (+11% em relação a Agosto); meta R$ 35.000, no alvo.
+• Novos clientes: 6 un (-14% em relação a Agosto); meta 6 un, no alvo.
+• Leads recebidos: 137 un (-4% em relação a Agosto); meta 120 un, no alvo.
+• Taxa de conversão de leads: 4,4 % (-10% em relação a Agosto); meta 5,0 %, abaixo da meta.
+• Ticket médio: R$ 9.700 (+3% em relação a Agosto); meta R$ 9.000, no alvo.
+• Inadimplência: 2,4 % (-8% em relação a Agosto); meta 3,0 %, no alvo.
+• Atendimentos realizados: 63 un (-5% em relação a Agosto); meta 60 un, no alvo.
+• NPS: 72 pts (-1% em relação a Agosto); meta 70 pts, no alvo.
+• Horas extras da equipe: 12 h (-14% em relação a Agosto); meta 20 h, no alvo.
+• Custo por lead: R$ 40,70 (+3% em relação a Agosto); meta R$ 45,00, no alvo.
+• Maior alta contra o mês anterior: Resultado (receita - despesas) (+11%).
+• Maior queda contra o mês anterior: Novos clientes (-14%).
+• Mais longe da meta: Taxa de conversão de leads (-12% da meta, abaixo da meta).
+• Indicadores no alvo: 10 de 12.</v>
       </c>
     </row>
     <row r="28">
@@ -2072,7 +2088,7 @@
       </c>
       <c r="B7" s="8">
         <f>MATCH(B6,Config!$D$5:$D$16,0)</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="D7" s="21" t="inlineStr">
         <is>
@@ -2086,9 +2102,9 @@
           <t>Mês anterior</t>
         </is>
       </c>
-      <c r="B8" s="8">
+      <c r="B8" s="8" t="str">
         <f>IF(B7&gt;1,INDEX($D$5:$D$16,B7-1),"")</f>
-        <v/>
+        <v>Agosto</v>
       </c>
       <c r="D8" s="21" t="inlineStr">
         <is>
@@ -2363,11 +2379,11 @@
       <c r="Q5" s="23" t="n"/>
       <c r="R5" s="9">
         <f>IF(COUNT(F5:Q5)=0,"",IF(OR(B5="%",B5="pts"),AVERAGE(F5:Q5),SUM(F5:Q5)))</f>
-        <v/>
+        <v>1033600</v>
       </c>
       <c r="S5" s="9">
         <f>IF(COUNT(F5:Q5)=0,"",AVERAGE(F5:Q5))</f>
-        <v/>
+        <v>114844.444444444</v>
       </c>
     </row>
     <row r="6">
@@ -2424,11 +2440,11 @@
       <c r="Q6" s="23" t="n"/>
       <c r="R6" s="9">
         <f>IF(COUNT(F6:Q6)=0,"",IF(OR(B6="%",B6="pts"),AVERAGE(F6:Q6),SUM(F6:Q6)))</f>
-        <v/>
+        <v>766600</v>
       </c>
       <c r="S6" s="9">
         <f>IF(COUNT(F6:Q6)=0,"",AVERAGE(F6:Q6))</f>
-        <v/>
+        <v>85177.7777777778</v>
       </c>
     </row>
     <row r="7">
@@ -2485,11 +2501,11 @@
       <c r="Q7" s="23" t="n"/>
       <c r="R7" s="9">
         <f>IF(COUNT(F7:Q7)=0,"",IF(OR(B7="%",B7="pts"),AVERAGE(F7:Q7),SUM(F7:Q7)))</f>
-        <v/>
+        <v>267000</v>
       </c>
       <c r="S7" s="9">
         <f>IF(COUNT(F7:Q7)=0,"",AVERAGE(F7:Q7))</f>
-        <v/>
+        <v>29666.6666666667</v>
       </c>
     </row>
     <row r="8">
@@ -2546,11 +2562,11 @@
       <c r="Q8" s="23" t="n"/>
       <c r="R8" s="9">
         <f>IF(COUNT(F8:Q8)=0,"",IF(OR(B8="%",B8="pts"),AVERAGE(F8:Q8),SUM(F8:Q8)))</f>
-        <v/>
+        <v>44</v>
       </c>
       <c r="S8" s="9">
         <f>IF(COUNT(F8:Q8)=0,"",AVERAGE(F8:Q8))</f>
-        <v/>
+        <v>4.88888888888889</v>
       </c>
     </row>
     <row r="9">
@@ -2607,11 +2623,11 @@
       <c r="Q9" s="23" t="n"/>
       <c r="R9" s="9">
         <f>IF(COUNT(F9:Q9)=0,"",IF(OR(B9="%",B9="pts"),AVERAGE(F9:Q9),SUM(F9:Q9)))</f>
-        <v/>
+        <v>1032</v>
       </c>
       <c r="S9" s="9">
         <f>IF(COUNT(F9:Q9)=0,"",AVERAGE(F9:Q9))</f>
-        <v/>
+        <v>114.666666666667</v>
       </c>
     </row>
     <row r="10">
@@ -2668,11 +2684,11 @@
       <c r="Q10" s="23" t="n"/>
       <c r="R10" s="9">
         <f>IF(COUNT(F10:Q10)=0,"",IF(OR(B10="%",B10="pts"),AVERAGE(F10:Q10),SUM(F10:Q10)))</f>
-        <v/>
+        <v>4.2</v>
       </c>
       <c r="S10" s="9">
         <f>IF(COUNT(F10:Q10)=0,"",AVERAGE(F10:Q10))</f>
-        <v/>
+        <v>4.2</v>
       </c>
     </row>
     <row r="11">
@@ -2729,11 +2745,11 @@
       <c r="Q11" s="23" t="n"/>
       <c r="R11" s="9">
         <f>IF(COUNT(F11:Q11)=0,"",IF(OR(B11="%",B11="pts"),AVERAGE(F11:Q11),SUM(F11:Q11)))</f>
-        <v/>
+        <v>80700</v>
       </c>
       <c r="S11" s="9">
         <f>IF(COUNT(F11:Q11)=0,"",AVERAGE(F11:Q11))</f>
-        <v/>
+        <v>8966.66666666667</v>
       </c>
     </row>
     <row r="12">
@@ -2790,11 +2806,11 @@
       <c r="Q12" s="23" t="n"/>
       <c r="R12" s="9">
         <f>IF(COUNT(F12:Q12)=0,"",IF(OR(B12="%",B12="pts"),AVERAGE(F12:Q12),SUM(F12:Q12)))</f>
-        <v/>
+        <v>3.22222222222222</v>
       </c>
       <c r="S12" s="9">
         <f>IF(COUNT(F12:Q12)=0,"",AVERAGE(F12:Q12))</f>
-        <v/>
+        <v>3.22222222222222</v>
       </c>
     </row>
     <row r="13">
@@ -2851,11 +2867,11 @@
       <c r="Q13" s="23" t="n"/>
       <c r="R13" s="9">
         <f>IF(COUNT(F13:Q13)=0,"",IF(OR(B13="%",B13="pts"),AVERAGE(F13:Q13),SUM(F13:Q13)))</f>
-        <v/>
+        <v>536</v>
       </c>
       <c r="S13" s="9">
         <f>IF(COUNT(F13:Q13)=0,"",AVERAGE(F13:Q13))</f>
-        <v/>
+        <v>59.5555555555556</v>
       </c>
     </row>
     <row r="14">
@@ -2912,11 +2928,11 @@
       <c r="Q14" s="23" t="n"/>
       <c r="R14" s="9">
         <f>IF(COUNT(F14:Q14)=0,"",IF(OR(B14="%",B14="pts"),AVERAGE(F14:Q14),SUM(F14:Q14)))</f>
-        <v/>
+        <v>68.8888888888889</v>
       </c>
       <c r="S14" s="9">
         <f>IF(COUNT(F14:Q14)=0,"",AVERAGE(F14:Q14))</f>
-        <v/>
+        <v>68.8888888888889</v>
       </c>
     </row>
     <row r="15">
@@ -2973,11 +2989,11 @@
       <c r="Q15" s="23" t="n"/>
       <c r="R15" s="9">
         <f>IF(COUNT(F15:Q15)=0,"",IF(OR(B15="%",B15="pts"),AVERAGE(F15:Q15),SUM(F15:Q15)))</f>
-        <v/>
+        <v>173</v>
       </c>
       <c r="S15" s="9">
         <f>IF(COUNT(F15:Q15)=0,"",AVERAGE(F15:Q15))</f>
-        <v/>
+        <v>19.2222222222222</v>
       </c>
     </row>
     <row r="16">
@@ -3034,11 +3050,11 @@
       <c r="Q16" s="23" t="n"/>
       <c r="R16" s="9">
         <f>IF(COUNT(F16:Q16)=0,"",IF(OR(B16="%",B16="pts"),AVERAGE(F16:Q16),SUM(F16:Q16)))</f>
-        <v/>
+        <v>405.8</v>
       </c>
       <c r="S16" s="9">
         <f>IF(COUNT(F16:Q16)=0,"",AVERAGE(F16:Q16))</f>
-        <v/>
+        <v>45.0888888888889</v>
       </c>
     </row>
     <row r="18">

--- a/projetos/gestao-ia-planilhas/produto/kit-essencial/entrega/02-relatorio-mensal-pronto.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-essencial/entrega/02-relatorio-mensal-pronto.xlsx
@@ -904,7 +904,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>A Prisma Comunicação é uma empresa fictícia. Os números são inventados. Apague-os antes de começar.</t>
+          <t>A Prisma Comunicação é uma empresa fictícia. Os números são inventados. Apague-os antes de começar. A planilha Ganhos e Gastos do kit usa outro exemplo, de uma autônoma, porque ela serve também para o dinheiro pessoal — não é descuido, é o uso previsto.</t>
         </is>
       </c>
     </row>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="H11" s="9">
         <f>IF(Indicadores!A11="","",Indicadores!R11)</f>
-        <v>80700</v>
+        <v>8966.66666666667</v>
       </c>
       <c r="I11" s="11" t="str">
         <f>IF(Indicadores!A11="","",Indicadores!B11)</f>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="H16" s="9">
         <f>IF(Indicadores!A16="","",Indicadores!R16)</f>
-        <v>405.8</v>
+        <v>45.0888888888889</v>
       </c>
       <c r="I16" s="11" t="str">
         <f>IF(Indicadores!A16="","",Indicadores!B16)</f>
@@ -1570,9 +1570,10 @@
           <t>Indicador do gráfico</t>
         </is>
       </c>
-      <c r="B18" s="14" t="str">
-        <f>Indicadores!A5</f>
-        <v>Receita</v>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>Receita</t>
+        </is>
       </c>
       <c r="C18" s="15" t="n"/>
       <c r="D18" s="16" t="n"/>
@@ -1792,7 +1793,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="B18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="B18" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" type="list">
       <formula1>=OFFSET(Indicadores!$A$5,0,0,MAX(1,COUNTA(Indicadores!$A$5:$A$16)),1)</formula1>
     </dataValidation>
   </dataValidations>
@@ -1929,7 +1930,7 @@
     </row>
     <row r="22">
       <c r="A22" s="19" t="str">
-        <f>IF(COUNT(Painel!$O$5:$O$16)=0,"• Nenhum indicador fora da meta.",IFERROR("• Mais longe da meta: "&amp;INDEX(Painel!$A$5:$A$16,MATCH(MAX(Painel!$O$5:$O$16),Painel!$O$5:$O$16,0))&amp;" ("&amp;IF(INDEX(Painel!$F$5:$F$16,MATCH(MAX(Painel!$O$5:$O$16),Painel!$O$5:$O$16,0))&gt;=0,"+","")&amp;FIXED(INDEX(Painel!$F$5:$F$16,MATCH(MAX(Painel!$O$5:$O$16),Painel!$O$5:$O$16,0))*100,0)&amp;"% da meta, "&amp;LOWER(INDEX(Painel!$G$5:$G$16,MATCH(MAX(Painel!$O$5:$O$16),Painel!$O$5:$O$16,0)))&amp;").",""))</f>
+        <f>IF((COUNTIF(Painel!$G$5:$G$16,"Acima da meta")+COUNTIF(Painel!$G$5:$G$16,"Abaixo da meta"))=0,"• Nenhum indicador fora da meta.",IF(COUNT(Painel!$O$5:$O$16)=0,"• "&amp;(COUNTIF(Painel!$G$5:$G$16,"Acima da meta")+COUNTIF(Painel!$G$5:$G$16,"Abaixo da meta"))&amp;" indicador(es) fora da meta (sem percentual: a meta é zero).",IFERROR("• Mais longe da meta: "&amp;INDEX(Painel!$A$5:$A$16,MATCH(MAX(Painel!$O$5:$O$16),Painel!$O$5:$O$16,0))&amp;" ("&amp;IF(INDEX(Painel!$F$5:$F$16,MATCH(MAX(Painel!$O$5:$O$16),Painel!$O$5:$O$16,0))&gt;=0,"+","")&amp;FIXED(INDEX(Painel!$F$5:$F$16,MATCH(MAX(Painel!$O$5:$O$16),Painel!$O$5:$O$16,0))*100,0)&amp;"% da meta, "&amp;LOWER(INDEX(Painel!$G$5:$G$16,MATCH(MAX(Painel!$O$5:$O$16),Painel!$O$5:$O$16,0)))&amp;").","")))</f>
         <v>• Mais longe da meta: Taxa de conversão de leads (-12% da meta, abaixo da meta).</v>
       </c>
     </row>
@@ -2176,7 +2177,7 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <dataValidations count="1">
-    <dataValidation sqref="B6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="B6" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" type="list">
       <formula1>=Config!$D$5:$D$16</formula1>
     </dataValidation>
   </dataValidations>
@@ -2190,7 +2191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S18"/>
+  <dimension ref="A1:T18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2316,12 +2317,17 @@
       </c>
       <c r="R4" s="7" t="inlineStr">
         <is>
-          <t>Acumulado (soma; média para % e pts)</t>
+          <t>Acumulado</t>
         </is>
       </c>
       <c r="S4" s="7" t="inlineStr">
         <is>
           <t>Média</t>
+        </is>
+      </c>
+      <c r="T4" s="7" t="inlineStr">
+        <is>
+          <t>Como acumular</t>
         </is>
       </c>
     </row>
@@ -2378,12 +2384,17 @@
       <c r="P5" s="23" t="n"/>
       <c r="Q5" s="23" t="n"/>
       <c r="R5" s="9">
-        <f>IF(COUNT(F5:Q5)=0,"",IF(OR(B5="%",B5="pts"),AVERAGE(F5:Q5),SUM(F5:Q5)))</f>
+        <f>IF(COUNT(F5:Q5)=0,"",IF(T5="Média",AVERAGE(F5:Q5),SUM(F5:Q5)))</f>
         <v>1033600</v>
       </c>
       <c r="S5" s="9">
         <f>IF(COUNT(F5:Q5)=0,"",AVERAGE(F5:Q5))</f>
         <v>114844.444444444</v>
+      </c>
+      <c r="T5" s="14" t="inlineStr">
+        <is>
+          <t>Soma</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -2439,12 +2450,17 @@
       <c r="P6" s="23" t="n"/>
       <c r="Q6" s="23" t="n"/>
       <c r="R6" s="9">
-        <f>IF(COUNT(F6:Q6)=0,"",IF(OR(B6="%",B6="pts"),AVERAGE(F6:Q6),SUM(F6:Q6)))</f>
+        <f>IF(COUNT(F6:Q6)=0,"",IF(T6="Média",AVERAGE(F6:Q6),SUM(F6:Q6)))</f>
         <v>766600</v>
       </c>
       <c r="S6" s="9">
         <f>IF(COUNT(F6:Q6)=0,"",AVERAGE(F6:Q6))</f>
         <v>85177.7777777778</v>
+      </c>
+      <c r="T6" s="14" t="inlineStr">
+        <is>
+          <t>Soma</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -2500,12 +2516,17 @@
       <c r="P7" s="23" t="n"/>
       <c r="Q7" s="23" t="n"/>
       <c r="R7" s="9">
-        <f>IF(COUNT(F7:Q7)=0,"",IF(OR(B7="%",B7="pts"),AVERAGE(F7:Q7),SUM(F7:Q7)))</f>
+        <f>IF(COUNT(F7:Q7)=0,"",IF(T7="Média",AVERAGE(F7:Q7),SUM(F7:Q7)))</f>
         <v>267000</v>
       </c>
       <c r="S7" s="9">
         <f>IF(COUNT(F7:Q7)=0,"",AVERAGE(F7:Q7))</f>
         <v>29666.6666666667</v>
+      </c>
+      <c r="T7" s="14" t="inlineStr">
+        <is>
+          <t>Soma</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -2561,12 +2582,17 @@
       <c r="P8" s="23" t="n"/>
       <c r="Q8" s="23" t="n"/>
       <c r="R8" s="9">
-        <f>IF(COUNT(F8:Q8)=0,"",IF(OR(B8="%",B8="pts"),AVERAGE(F8:Q8),SUM(F8:Q8)))</f>
+        <f>IF(COUNT(F8:Q8)=0,"",IF(T8="Média",AVERAGE(F8:Q8),SUM(F8:Q8)))</f>
         <v>44</v>
       </c>
       <c r="S8" s="9">
         <f>IF(COUNT(F8:Q8)=0,"",AVERAGE(F8:Q8))</f>
         <v>4.88888888888889</v>
+      </c>
+      <c r="T8" s="14" t="inlineStr">
+        <is>
+          <t>Soma</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -2622,12 +2648,17 @@
       <c r="P9" s="23" t="n"/>
       <c r="Q9" s="23" t="n"/>
       <c r="R9" s="9">
-        <f>IF(COUNT(F9:Q9)=0,"",IF(OR(B9="%",B9="pts"),AVERAGE(F9:Q9),SUM(F9:Q9)))</f>
+        <f>IF(COUNT(F9:Q9)=0,"",IF(T9="Média",AVERAGE(F9:Q9),SUM(F9:Q9)))</f>
         <v>1032</v>
       </c>
       <c r="S9" s="9">
         <f>IF(COUNT(F9:Q9)=0,"",AVERAGE(F9:Q9))</f>
         <v>114.666666666667</v>
+      </c>
+      <c r="T9" s="14" t="inlineStr">
+        <is>
+          <t>Soma</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -2683,12 +2714,17 @@
       <c r="P10" s="23" t="n"/>
       <c r="Q10" s="23" t="n"/>
       <c r="R10" s="9">
-        <f>IF(COUNT(F10:Q10)=0,"",IF(OR(B10="%",B10="pts"),AVERAGE(F10:Q10),SUM(F10:Q10)))</f>
+        <f>IF(COUNT(F10:Q10)=0,"",IF(T10="Média",AVERAGE(F10:Q10),SUM(F10:Q10)))</f>
         <v>4.2</v>
       </c>
       <c r="S10" s="9">
         <f>IF(COUNT(F10:Q10)=0,"",AVERAGE(F10:Q10))</f>
         <v>4.2</v>
+      </c>
+      <c r="T10" s="14" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -2744,12 +2780,17 @@
       <c r="P11" s="23" t="n"/>
       <c r="Q11" s="23" t="n"/>
       <c r="R11" s="9">
-        <f>IF(COUNT(F11:Q11)=0,"",IF(OR(B11="%",B11="pts"),AVERAGE(F11:Q11),SUM(F11:Q11)))</f>
-        <v>80700</v>
+        <f>IF(COUNT(F11:Q11)=0,"",IF(T11="Média",AVERAGE(F11:Q11),SUM(F11:Q11)))</f>
+        <v>8966.66666666667</v>
       </c>
       <c r="S11" s="9">
         <f>IF(COUNT(F11:Q11)=0,"",AVERAGE(F11:Q11))</f>
         <v>8966.66666666667</v>
+      </c>
+      <c r="T11" s="14" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -2805,12 +2846,17 @@
       <c r="P12" s="23" t="n"/>
       <c r="Q12" s="23" t="n"/>
       <c r="R12" s="9">
-        <f>IF(COUNT(F12:Q12)=0,"",IF(OR(B12="%",B12="pts"),AVERAGE(F12:Q12),SUM(F12:Q12)))</f>
+        <f>IF(COUNT(F12:Q12)=0,"",IF(T12="Média",AVERAGE(F12:Q12),SUM(F12:Q12)))</f>
         <v>3.22222222222222</v>
       </c>
       <c r="S12" s="9">
         <f>IF(COUNT(F12:Q12)=0,"",AVERAGE(F12:Q12))</f>
         <v>3.22222222222222</v>
+      </c>
+      <c r="T12" s="14" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -2866,12 +2912,17 @@
       <c r="P13" s="23" t="n"/>
       <c r="Q13" s="23" t="n"/>
       <c r="R13" s="9">
-        <f>IF(COUNT(F13:Q13)=0,"",IF(OR(B13="%",B13="pts"),AVERAGE(F13:Q13),SUM(F13:Q13)))</f>
+        <f>IF(COUNT(F13:Q13)=0,"",IF(T13="Média",AVERAGE(F13:Q13),SUM(F13:Q13)))</f>
         <v>536</v>
       </c>
       <c r="S13" s="9">
         <f>IF(COUNT(F13:Q13)=0,"",AVERAGE(F13:Q13))</f>
         <v>59.5555555555556</v>
+      </c>
+      <c r="T13" s="14" t="inlineStr">
+        <is>
+          <t>Soma</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -2927,12 +2978,17 @@
       <c r="P14" s="23" t="n"/>
       <c r="Q14" s="23" t="n"/>
       <c r="R14" s="9">
-        <f>IF(COUNT(F14:Q14)=0,"",IF(OR(B14="%",B14="pts"),AVERAGE(F14:Q14),SUM(F14:Q14)))</f>
+        <f>IF(COUNT(F14:Q14)=0,"",IF(T14="Média",AVERAGE(F14:Q14),SUM(F14:Q14)))</f>
         <v>68.8888888888889</v>
       </c>
       <c r="S14" s="9">
         <f>IF(COUNT(F14:Q14)=0,"",AVERAGE(F14:Q14))</f>
         <v>68.8888888888889</v>
+      </c>
+      <c r="T14" s="14" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -2988,12 +3044,17 @@
       <c r="P15" s="23" t="n"/>
       <c r="Q15" s="23" t="n"/>
       <c r="R15" s="9">
-        <f>IF(COUNT(F15:Q15)=0,"",IF(OR(B15="%",B15="pts"),AVERAGE(F15:Q15),SUM(F15:Q15)))</f>
+        <f>IF(COUNT(F15:Q15)=0,"",IF(T15="Média",AVERAGE(F15:Q15),SUM(F15:Q15)))</f>
         <v>173</v>
       </c>
       <c r="S15" s="9">
         <f>IF(COUNT(F15:Q15)=0,"",AVERAGE(F15:Q15))</f>
         <v>19.2222222222222</v>
+      </c>
+      <c r="T15" s="14" t="inlineStr">
+        <is>
+          <t>Soma</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -3049,36 +3110,44 @@
       <c r="P16" s="23" t="n"/>
       <c r="Q16" s="23" t="n"/>
       <c r="R16" s="9">
-        <f>IF(COUNT(F16:Q16)=0,"",IF(OR(B16="%",B16="pts"),AVERAGE(F16:Q16),SUM(F16:Q16)))</f>
-        <v>405.8</v>
+        <f>IF(COUNT(F16:Q16)=0,"",IF(T16="Média",AVERAGE(F16:Q16),SUM(F16:Q16)))</f>
+        <v>45.0888888888889</v>
       </c>
       <c r="S16" s="9">
         <f>IF(COUNT(F16:Q16)=0,"",AVERAGE(F16:Q16))</f>
         <v>45.0888888888889</v>
       </c>
+      <c r="T16" s="14" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>"Acumulado" soma os meses preenchidos quando a unidade é R$, un ou h; quando é % ou pts (taxas, notas), mostra a média dos meses, porque somar taxas não faz sentido. "Média" é sempre a média. Para indicadores em %, digite 4,5 (não 0,045).</t>
+          <t>"Como acumular" decide o que o Acumulado mostra: Soma para o que se empilha (receita, despesa, quantidade, horas) e Média para razão (ticket médio, custo por lead, taxa, nota). Somar razão não significa nada: doze meses de ticket médio somados não são o ticket do ano. "Média" é sempre a média dos meses preenchidos. Para indicadores em %, digite 4,5 (não 0,045).</t>
         </is>
       </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="2">
-    <mergeCell ref="A18:S18"/>
+    <mergeCell ref="A18:T18"/>
     <mergeCell ref="A2:R2"/>
   </mergeCells>
-  <dataValidations count="3">
-    <dataValidation sqref="E5:E16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+  <dataValidations count="4">
+    <dataValidation sqref="E5:E16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Sim,Não"</formula1>
     </dataValidation>
-    <dataValidation sqref="C5:C16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C5:C16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"0,1,2"</formula1>
     </dataValidation>
-    <dataValidation sqref="B5:B16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B5:B16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"R$,%,un,h,pts"</formula1>
+    </dataValidation>
+    <dataValidation sqref="T5:T16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Como acumular" error="Escolha Soma (empilha) ou Média (razão)." type="list">
+      <formula1>"Soma,Média"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/projetos/gestao-ia-planilhas/produto/kit-essencial/entrega/02-relatorio-mensal-pronto.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-essencial/entrega/02-relatorio-mensal-pronto.xlsx
@@ -767,7 +767,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -796,125 +796,137 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Você digita até 12 indicadores por mês; ela calcula variação contra o mês anterior, comparação com a meta, acumulado (soma; média para % e pts) e média, monta o painel e escreve as frases-base do relatório para você colar na IA.</t>
+          <t>Você digita até 12 indicadores por mês; ela calcula variação contra o mês anterior, comparação com a meta, acumulado, média, monta o painel e escreve as frases-base do relatório para você colar na IA.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="46" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Passo 1</t>
+          <t>Como acumular</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Em Config, preencha o nome da empresa ou área, o ano e escolha o mês do relatório.</t>
+          <t>Cada indicador tem a sua regra, escolhida na última coluna da aba Indicadores: "Soma" para o que se empilha (receita, despesa, quantidade, horas) e "Média" para razão (ticket médio, custo por lead, taxa de conversão, inadimplência, NPS) — inclusive quando a razão está em reais. Somar razão não significa nada: doze meses de ticket médio somados não são o ticket do ano. A Média usa só os meses preenchidos; um mês com zero digitado ENTRA na conta, um mês em branco não.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="46" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Passo 2</t>
+          <t>Passo 1</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Em Indicadores, troque os exemplos pelos seus (de cima para baixo, sem pular linha): nome, unidade (R$, %, un, h, pts), casas decimais, meta mensal e se maior é melhor. Depois, o valor de cada mês. Em %, digite 4,5 e não 0,045.</t>
+          <t>Em Config, preencha o nome da empresa ou área, o ano e escolha o mês do relatório.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="46" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Passo 3</t>
+          <t>Passo 2</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Abra Painel: cada indicador com mês, mês anterior, variação, meta e situação (verde no alvo, vermelho fora). Escolha um indicador para o gráfico de evolução.</t>
+          <t>Em Indicadores, troque os exemplos pelos seus (de cima para baixo, sem pular linha): nome, unidade (R$, %, un, h, pts), casas decimais, meta mensal e se maior é melhor. Depois, o valor de cada mês. Em %, digite 4,5 e não 0,045.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="46" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Passo 4</t>
+          <t>Passo 3</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Abra Resumo: as frases do mês já estão escritas. Copie o bloco único e cole no prompt "Escrever 01" (relatório executivo) ou "Apresentar 01" (roteiro de 8 slides) da biblioteca do kit, junto com os seus comentários sobre o porquê dos números.</t>
+          <t>Abra Painel: cada indicador com mês, mês anterior, variação, meta e situação (verde no alvo, vermelho fora). Escolha um indicador para o gráfico de evolução.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="46" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Todo mês</t>
+          <t>Passo 4</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Digite os valores do novo mês em Indicadores e troque o mês em Config. O resto se refaz sozinho.</t>
+          <t>Abra Resumo: as frases do mês já estão escritas. Copie o bloco único e cole no prompt "Escrever 01" (relatório executivo) ou "Apresentar 01" (roteiro de 8 slides) da biblioteca do kit, junto com os seus comentários sobre o porquê dos números.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="46" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Legenda</t>
+          <t>Todo mês</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Células amarelas: você preenche. Células brancas: calculadas. Verde: no alvo. Vermelho: fora da meta.</t>
+          <t>Digite os valores do novo mês em Indicadores e troque o mês em Config. O resto se refaz sozinho.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="46" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Proteção</t>
+          <t>Legenda</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Fórmulas protegidas sem senha. Para editar: Revisar &gt; Desproteger planilha (Excel) ou Dados &gt; Proteger intervalos (Google Sheets).</t>
+          <t>Células amarelas: você preenche. Células brancas: calculadas. Verde: no alvo. Vermelho: fora da meta.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="46" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Google Sheets</t>
+          <t>Proteção</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores e gráfico funcionam.</t>
+          <t>Fórmulas protegidas sem senha. Para editar: Revisar &gt; Desproteger planilha (Excel) ou Dados &gt; Proteger intervalos (Google Sheets).</t>
         </is>
       </c>
     </row>
     <row r="13" ht="46" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Exemplos</t>
+          <t>Google Sheets</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>A Prisma Comunicação é uma empresa fictícia. Os números são inventados. Apague-os antes de começar. A planilha Ganhos e Gastos do kit usa outro exemplo, de uma autônoma, porque ela serve também para o dinheiro pessoal — não é descuido, é o uso previsto.</t>
+          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores e gráfico funcionam.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="46" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
+          <t>Exemplos</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>A Prisma Comunicação é uma empresa fictícia. Os números são inventados. Apague-os antes de começar. A planilha Ganhos e Gastos do kit usa outro exemplo, de uma autônoma, porque ela serve também para o dinheiro pessoal — não é descuido, é o uso previsto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="46" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
           <t>Suporte</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>suporte@seusociogestor.com.br · resposta em até 5 dias úteis · reembolso em até 7 dias pelo mesmo canal.</t>
         </is>
@@ -1839,73 +1851,73 @@
     </row>
     <row r="6">
       <c r="A6" s="19" t="str">
-        <f>IF(OR(Indicadores!A5="",Painel!B5=""),"","• "&amp;Indicadores!A5&amp;": "&amp;IF(Indicadores!B5="R$","R$ ","")&amp;FIXED(Painel!B5,IF(Indicadores!C5="",0,Indicadores!C5))&amp;IF(OR(Indicadores!B5="R$",Indicadores!B5=""),""," "&amp;Indicadores!B5)&amp;IF(Painel!C5&lt;&gt;"",IF(Painel!D5&gt;=0," (+"," (")&amp;FIXED(Painel!D5*100,0)&amp;"% em relação a "&amp;Config!$B$8&amp;")","")&amp;IF(Painel!E5&lt;&gt;"","; meta "&amp;IF(Indicadores!B5="R$","R$ ","")&amp;FIXED(Painel!E5,IF(Indicadores!C5="",0,Indicadores!C5))&amp;IF(OR(Indicadores!B5="R$",Indicadores!B5=""),""," "&amp;Indicadores!B5)&amp;", "&amp;LOWER(Painel!G5),"")&amp;".")</f>
+        <f>IF(OR(Indicadores!A5="",Painel!B5=""),"","• "&amp;Indicadores!A5&amp;": "&amp;IF(Indicadores!B5="R$","R$ ","")&amp;FIXED(Painel!B5,IF(Indicadores!C5="",0,Indicadores!C5))&amp;IF(OR(Indicadores!B5="R$",Indicadores!B5=""),""," "&amp;Indicadores!B5)&amp;IF(Painel!C5="","",IF(AND(Painel!C5=0,Painel!B5&lt;&gt;0)," (sem base de comparação: "&amp;Config!$B$8&amp;" foi zero)",IF(Painel!D5="","",IF(Painel!D5&gt;=0," (+"," (")&amp;FIXED(Painel!D5*100,0)&amp;"% em relação a "&amp;Config!$B$8&amp;")")))&amp;IF(Painel!E5&lt;&gt;"","; meta "&amp;IF(Indicadores!B5="R$","R$ ","")&amp;FIXED(Painel!E5,IF(Indicadores!C5="",0,Indicadores!C5))&amp;IF(OR(Indicadores!B5="R$",Indicadores!B5=""),""," "&amp;Indicadores!B5)&amp;", "&amp;LOWER(Painel!G5),"")&amp;".")</f>
         <v>• Receita: R$ 131.200 (+5% em relação a Agosto); meta R$ 120.000, no alvo.</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="19" t="str">
-        <f>IF(OR(Indicadores!A6="",Painel!B6=""),"","• "&amp;Indicadores!A6&amp;": "&amp;IF(Indicadores!B6="R$","R$ ","")&amp;FIXED(Painel!B6,IF(Indicadores!C6="",0,Indicadores!C6))&amp;IF(OR(Indicadores!B6="R$",Indicadores!B6=""),""," "&amp;Indicadores!B6)&amp;IF(Painel!C6&lt;&gt;"",IF(Painel!D6&gt;=0," (+"," (")&amp;FIXED(Painel!D6*100,0)&amp;"% em relação a "&amp;Config!$B$8&amp;")","")&amp;IF(Painel!E6&lt;&gt;"","; meta "&amp;IF(Indicadores!B6="R$","R$ ","")&amp;FIXED(Painel!E6,IF(Indicadores!C6="",0,Indicadores!C6))&amp;IF(OR(Indicadores!B6="R$",Indicadores!B6=""),""," "&amp;Indicadores!B6)&amp;", "&amp;LOWER(Painel!G6),"")&amp;".")</f>
+        <f>IF(OR(Indicadores!A6="",Painel!B6=""),"","• "&amp;Indicadores!A6&amp;": "&amp;IF(Indicadores!B6="R$","R$ ","")&amp;FIXED(Painel!B6,IF(Indicadores!C6="",0,Indicadores!C6))&amp;IF(OR(Indicadores!B6="R$",Indicadores!B6=""),""," "&amp;Indicadores!B6)&amp;IF(Painel!C6="","",IF(AND(Painel!C6=0,Painel!B6&lt;&gt;0)," (sem base de comparação: "&amp;Config!$B$8&amp;" foi zero)",IF(Painel!D6="","",IF(Painel!D6&gt;=0," (+"," (")&amp;FIXED(Painel!D6*100,0)&amp;"% em relação a "&amp;Config!$B$8&amp;")")))&amp;IF(Painel!E6&lt;&gt;"","; meta "&amp;IF(Indicadores!B6="R$","R$ ","")&amp;FIXED(Painel!E6,IF(Indicadores!C6="",0,Indicadores!C6))&amp;IF(OR(Indicadores!B6="R$",Indicadores!B6=""),""," "&amp;Indicadores!B6)&amp;", "&amp;LOWER(Painel!G6),"")&amp;".")</f>
         <v>• Despesas: R$ 89.800 (+3% em relação a Agosto); meta R$ 85.000, acima da meta.</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="19" t="str">
-        <f>IF(OR(Indicadores!A7="",Painel!B7=""),"","• "&amp;Indicadores!A7&amp;": "&amp;IF(Indicadores!B7="R$","R$ ","")&amp;FIXED(Painel!B7,IF(Indicadores!C7="",0,Indicadores!C7))&amp;IF(OR(Indicadores!B7="R$",Indicadores!B7=""),""," "&amp;Indicadores!B7)&amp;IF(Painel!C7&lt;&gt;"",IF(Painel!D7&gt;=0," (+"," (")&amp;FIXED(Painel!D7*100,0)&amp;"% em relação a "&amp;Config!$B$8&amp;")","")&amp;IF(Painel!E7&lt;&gt;"","; meta "&amp;IF(Indicadores!B7="R$","R$ ","")&amp;FIXED(Painel!E7,IF(Indicadores!C7="",0,Indicadores!C7))&amp;IF(OR(Indicadores!B7="R$",Indicadores!B7=""),""," "&amp;Indicadores!B7)&amp;", "&amp;LOWER(Painel!G7),"")&amp;".")</f>
+        <f>IF(OR(Indicadores!A7="",Painel!B7=""),"","• "&amp;Indicadores!A7&amp;": "&amp;IF(Indicadores!B7="R$","R$ ","")&amp;FIXED(Painel!B7,IF(Indicadores!C7="",0,Indicadores!C7))&amp;IF(OR(Indicadores!B7="R$",Indicadores!B7=""),""," "&amp;Indicadores!B7)&amp;IF(Painel!C7="","",IF(AND(Painel!C7=0,Painel!B7&lt;&gt;0)," (sem base de comparação: "&amp;Config!$B$8&amp;" foi zero)",IF(Painel!D7="","",IF(Painel!D7&gt;=0," (+"," (")&amp;FIXED(Painel!D7*100,0)&amp;"% em relação a "&amp;Config!$B$8&amp;")")))&amp;IF(Painel!E7&lt;&gt;"","; meta "&amp;IF(Indicadores!B7="R$","R$ ","")&amp;FIXED(Painel!E7,IF(Indicadores!C7="",0,Indicadores!C7))&amp;IF(OR(Indicadores!B7="R$",Indicadores!B7=""),""," "&amp;Indicadores!B7)&amp;", "&amp;LOWER(Painel!G7),"")&amp;".")</f>
         <v>• Resultado (receita - despesas): R$ 41.400 (+11% em relação a Agosto); meta R$ 35.000, no alvo.</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="19" t="str">
-        <f>IF(OR(Indicadores!A8="",Painel!B8=""),"","• "&amp;Indicadores!A8&amp;": "&amp;IF(Indicadores!B8="R$","R$ ","")&amp;FIXED(Painel!B8,IF(Indicadores!C8="",0,Indicadores!C8))&amp;IF(OR(Indicadores!B8="R$",Indicadores!B8=""),""," "&amp;Indicadores!B8)&amp;IF(Painel!C8&lt;&gt;"",IF(Painel!D8&gt;=0," (+"," (")&amp;FIXED(Painel!D8*100,0)&amp;"% em relação a "&amp;Config!$B$8&amp;")","")&amp;IF(Painel!E8&lt;&gt;"","; meta "&amp;IF(Indicadores!B8="R$","R$ ","")&amp;FIXED(Painel!E8,IF(Indicadores!C8="",0,Indicadores!C8))&amp;IF(OR(Indicadores!B8="R$",Indicadores!B8=""),""," "&amp;Indicadores!B8)&amp;", "&amp;LOWER(Painel!G8),"")&amp;".")</f>
+        <f>IF(OR(Indicadores!A8="",Painel!B8=""),"","• "&amp;Indicadores!A8&amp;": "&amp;IF(Indicadores!B8="R$","R$ ","")&amp;FIXED(Painel!B8,IF(Indicadores!C8="",0,Indicadores!C8))&amp;IF(OR(Indicadores!B8="R$",Indicadores!B8=""),""," "&amp;Indicadores!B8)&amp;IF(Painel!C8="","",IF(AND(Painel!C8=0,Painel!B8&lt;&gt;0)," (sem base de comparação: "&amp;Config!$B$8&amp;" foi zero)",IF(Painel!D8="","",IF(Painel!D8&gt;=0," (+"," (")&amp;FIXED(Painel!D8*100,0)&amp;"% em relação a "&amp;Config!$B$8&amp;")")))&amp;IF(Painel!E8&lt;&gt;"","; meta "&amp;IF(Indicadores!B8="R$","R$ ","")&amp;FIXED(Painel!E8,IF(Indicadores!C8="",0,Indicadores!C8))&amp;IF(OR(Indicadores!B8="R$",Indicadores!B8=""),""," "&amp;Indicadores!B8)&amp;", "&amp;LOWER(Painel!G8),"")&amp;".")</f>
         <v>• Novos clientes: 6 un (-14% em relação a Agosto); meta 6 un, no alvo.</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="19" t="str">
-        <f>IF(OR(Indicadores!A9="",Painel!B9=""),"","• "&amp;Indicadores!A9&amp;": "&amp;IF(Indicadores!B9="R$","R$ ","")&amp;FIXED(Painel!B9,IF(Indicadores!C9="",0,Indicadores!C9))&amp;IF(OR(Indicadores!B9="R$",Indicadores!B9=""),""," "&amp;Indicadores!B9)&amp;IF(Painel!C9&lt;&gt;"",IF(Painel!D9&gt;=0," (+"," (")&amp;FIXED(Painel!D9*100,0)&amp;"% em relação a "&amp;Config!$B$8&amp;")","")&amp;IF(Painel!E9&lt;&gt;"","; meta "&amp;IF(Indicadores!B9="R$","R$ ","")&amp;FIXED(Painel!E9,IF(Indicadores!C9="",0,Indicadores!C9))&amp;IF(OR(Indicadores!B9="R$",Indicadores!B9=""),""," "&amp;Indicadores!B9)&amp;", "&amp;LOWER(Painel!G9),"")&amp;".")</f>
+        <f>IF(OR(Indicadores!A9="",Painel!B9=""),"","• "&amp;Indicadores!A9&amp;": "&amp;IF(Indicadores!B9="R$","R$ ","")&amp;FIXED(Painel!B9,IF(Indicadores!C9="",0,Indicadores!C9))&amp;IF(OR(Indicadores!B9="R$",Indicadores!B9=""),""," "&amp;Indicadores!B9)&amp;IF(Painel!C9="","",IF(AND(Painel!C9=0,Painel!B9&lt;&gt;0)," (sem base de comparação: "&amp;Config!$B$8&amp;" foi zero)",IF(Painel!D9="","",IF(Painel!D9&gt;=0," (+"," (")&amp;FIXED(Painel!D9*100,0)&amp;"% em relação a "&amp;Config!$B$8&amp;")")))&amp;IF(Painel!E9&lt;&gt;"","; meta "&amp;IF(Indicadores!B9="R$","R$ ","")&amp;FIXED(Painel!E9,IF(Indicadores!C9="",0,Indicadores!C9))&amp;IF(OR(Indicadores!B9="R$",Indicadores!B9=""),""," "&amp;Indicadores!B9)&amp;", "&amp;LOWER(Painel!G9),"")&amp;".")</f>
         <v>• Leads recebidos: 137 un (-4% em relação a Agosto); meta 120 un, no alvo.</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="19" t="str">
-        <f>IF(OR(Indicadores!A10="",Painel!B10=""),"","• "&amp;Indicadores!A10&amp;": "&amp;IF(Indicadores!B10="R$","R$ ","")&amp;FIXED(Painel!B10,IF(Indicadores!C10="",0,Indicadores!C10))&amp;IF(OR(Indicadores!B10="R$",Indicadores!B10=""),""," "&amp;Indicadores!B10)&amp;IF(Painel!C10&lt;&gt;"",IF(Painel!D10&gt;=0," (+"," (")&amp;FIXED(Painel!D10*100,0)&amp;"% em relação a "&amp;Config!$B$8&amp;")","")&amp;IF(Painel!E10&lt;&gt;"","; meta "&amp;IF(Indicadores!B10="R$","R$ ","")&amp;FIXED(Painel!E10,IF(Indicadores!C10="",0,Indicadores!C10))&amp;IF(OR(Indicadores!B10="R$",Indicadores!B10=""),""," "&amp;Indicadores!B10)&amp;", "&amp;LOWER(Painel!G10),"")&amp;".")</f>
+        <f>IF(OR(Indicadores!A10="",Painel!B10=""),"","• "&amp;Indicadores!A10&amp;": "&amp;IF(Indicadores!B10="R$","R$ ","")&amp;FIXED(Painel!B10,IF(Indicadores!C10="",0,Indicadores!C10))&amp;IF(OR(Indicadores!B10="R$",Indicadores!B10=""),""," "&amp;Indicadores!B10)&amp;IF(Painel!C10="","",IF(AND(Painel!C10=0,Painel!B10&lt;&gt;0)," (sem base de comparação: "&amp;Config!$B$8&amp;" foi zero)",IF(Painel!D10="","",IF(Painel!D10&gt;=0," (+"," (")&amp;FIXED(Painel!D10*100,0)&amp;"% em relação a "&amp;Config!$B$8&amp;")")))&amp;IF(Painel!E10&lt;&gt;"","; meta "&amp;IF(Indicadores!B10="R$","R$ ","")&amp;FIXED(Painel!E10,IF(Indicadores!C10="",0,Indicadores!C10))&amp;IF(OR(Indicadores!B10="R$",Indicadores!B10=""),""," "&amp;Indicadores!B10)&amp;", "&amp;LOWER(Painel!G10),"")&amp;".")</f>
         <v>• Taxa de conversão de leads: 4,4 % (-10% em relação a Agosto); meta 5,0 %, abaixo da meta.</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="19" t="str">
-        <f>IF(OR(Indicadores!A11="",Painel!B11=""),"","• "&amp;Indicadores!A11&amp;": "&amp;IF(Indicadores!B11="R$","R$ ","")&amp;FIXED(Painel!B11,IF(Indicadores!C11="",0,Indicadores!C11))&amp;IF(OR(Indicadores!B11="R$",Indicadores!B11=""),""," "&amp;Indicadores!B11)&amp;IF(Painel!C11&lt;&gt;"",IF(Painel!D11&gt;=0," (+"," (")&amp;FIXED(Painel!D11*100,0)&amp;"% em relação a "&amp;Config!$B$8&amp;")","")&amp;IF(Painel!E11&lt;&gt;"","; meta "&amp;IF(Indicadores!B11="R$","R$ ","")&amp;FIXED(Painel!E11,IF(Indicadores!C11="",0,Indicadores!C11))&amp;IF(OR(Indicadores!B11="R$",Indicadores!B11=""),""," "&amp;Indicadores!B11)&amp;", "&amp;LOWER(Painel!G11),"")&amp;".")</f>
+        <f>IF(OR(Indicadores!A11="",Painel!B11=""),"","• "&amp;Indicadores!A11&amp;": "&amp;IF(Indicadores!B11="R$","R$ ","")&amp;FIXED(Painel!B11,IF(Indicadores!C11="",0,Indicadores!C11))&amp;IF(OR(Indicadores!B11="R$",Indicadores!B11=""),""," "&amp;Indicadores!B11)&amp;IF(Painel!C11="","",IF(AND(Painel!C11=0,Painel!B11&lt;&gt;0)," (sem base de comparação: "&amp;Config!$B$8&amp;" foi zero)",IF(Painel!D11="","",IF(Painel!D11&gt;=0," (+"," (")&amp;FIXED(Painel!D11*100,0)&amp;"% em relação a "&amp;Config!$B$8&amp;")")))&amp;IF(Painel!E11&lt;&gt;"","; meta "&amp;IF(Indicadores!B11="R$","R$ ","")&amp;FIXED(Painel!E11,IF(Indicadores!C11="",0,Indicadores!C11))&amp;IF(OR(Indicadores!B11="R$",Indicadores!B11=""),""," "&amp;Indicadores!B11)&amp;", "&amp;LOWER(Painel!G11),"")&amp;".")</f>
         <v>• Ticket médio: R$ 9.700 (+3% em relação a Agosto); meta R$ 9.000, no alvo.</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="19" t="str">
-        <f>IF(OR(Indicadores!A12="",Painel!B12=""),"","• "&amp;Indicadores!A12&amp;": "&amp;IF(Indicadores!B12="R$","R$ ","")&amp;FIXED(Painel!B12,IF(Indicadores!C12="",0,Indicadores!C12))&amp;IF(OR(Indicadores!B12="R$",Indicadores!B12=""),""," "&amp;Indicadores!B12)&amp;IF(Painel!C12&lt;&gt;"",IF(Painel!D12&gt;=0," (+"," (")&amp;FIXED(Painel!D12*100,0)&amp;"% em relação a "&amp;Config!$B$8&amp;")","")&amp;IF(Painel!E12&lt;&gt;"","; meta "&amp;IF(Indicadores!B12="R$","R$ ","")&amp;FIXED(Painel!E12,IF(Indicadores!C12="",0,Indicadores!C12))&amp;IF(OR(Indicadores!B12="R$",Indicadores!B12=""),""," "&amp;Indicadores!B12)&amp;", "&amp;LOWER(Painel!G12),"")&amp;".")</f>
+        <f>IF(OR(Indicadores!A12="",Painel!B12=""),"","• "&amp;Indicadores!A12&amp;": "&amp;IF(Indicadores!B12="R$","R$ ","")&amp;FIXED(Painel!B12,IF(Indicadores!C12="",0,Indicadores!C12))&amp;IF(OR(Indicadores!B12="R$",Indicadores!B12=""),""," "&amp;Indicadores!B12)&amp;IF(Painel!C12="","",IF(AND(Painel!C12=0,Painel!B12&lt;&gt;0)," (sem base de comparação: "&amp;Config!$B$8&amp;" foi zero)",IF(Painel!D12="","",IF(Painel!D12&gt;=0," (+"," (")&amp;FIXED(Painel!D12*100,0)&amp;"% em relação a "&amp;Config!$B$8&amp;")")))&amp;IF(Painel!E12&lt;&gt;"","; meta "&amp;IF(Indicadores!B12="R$","R$ ","")&amp;FIXED(Painel!E12,IF(Indicadores!C12="",0,Indicadores!C12))&amp;IF(OR(Indicadores!B12="R$",Indicadores!B12=""),""," "&amp;Indicadores!B12)&amp;", "&amp;LOWER(Painel!G12),"")&amp;".")</f>
         <v>• Inadimplência: 2,4 % (-8% em relação a Agosto); meta 3,0 %, no alvo.</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="19" t="str">
-        <f>IF(OR(Indicadores!A13="",Painel!B13=""),"","• "&amp;Indicadores!A13&amp;": "&amp;IF(Indicadores!B13="R$","R$ ","")&amp;FIXED(Painel!B13,IF(Indicadores!C13="",0,Indicadores!C13))&amp;IF(OR(Indicadores!B13="R$",Indicadores!B13=""),""," "&amp;Indicadores!B13)&amp;IF(Painel!C13&lt;&gt;"",IF(Painel!D13&gt;=0," (+"," (")&amp;FIXED(Painel!D13*100,0)&amp;"% em relação a "&amp;Config!$B$8&amp;")","")&amp;IF(Painel!E13&lt;&gt;"","; meta "&amp;IF(Indicadores!B13="R$","R$ ","")&amp;FIXED(Painel!E13,IF(Indicadores!C13="",0,Indicadores!C13))&amp;IF(OR(Indicadores!B13="R$",Indicadores!B13=""),""," "&amp;Indicadores!B13)&amp;", "&amp;LOWER(Painel!G13),"")&amp;".")</f>
+        <f>IF(OR(Indicadores!A13="",Painel!B13=""),"","• "&amp;Indicadores!A13&amp;": "&amp;IF(Indicadores!B13="R$","R$ ","")&amp;FIXED(Painel!B13,IF(Indicadores!C13="",0,Indicadores!C13))&amp;IF(OR(Indicadores!B13="R$",Indicadores!B13=""),""," "&amp;Indicadores!B13)&amp;IF(Painel!C13="","",IF(AND(Painel!C13=0,Painel!B13&lt;&gt;0)," (sem base de comparação: "&amp;Config!$B$8&amp;" foi zero)",IF(Painel!D13="","",IF(Painel!D13&gt;=0," (+"," (")&amp;FIXED(Painel!D13*100,0)&amp;"% em relação a "&amp;Config!$B$8&amp;")")))&amp;IF(Painel!E13&lt;&gt;"","; meta "&amp;IF(Indicadores!B13="R$","R$ ","")&amp;FIXED(Painel!E13,IF(Indicadores!C13="",0,Indicadores!C13))&amp;IF(OR(Indicadores!B13="R$",Indicadores!B13=""),""," "&amp;Indicadores!B13)&amp;", "&amp;LOWER(Painel!G13),"")&amp;".")</f>
         <v>• Atendimentos realizados: 63 un (-5% em relação a Agosto); meta 60 un, no alvo.</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="19" t="str">
-        <f>IF(OR(Indicadores!A14="",Painel!B14=""),"","• "&amp;Indicadores!A14&amp;": "&amp;IF(Indicadores!B14="R$","R$ ","")&amp;FIXED(Painel!B14,IF(Indicadores!C14="",0,Indicadores!C14))&amp;IF(OR(Indicadores!B14="R$",Indicadores!B14=""),""," "&amp;Indicadores!B14)&amp;IF(Painel!C14&lt;&gt;"",IF(Painel!D14&gt;=0," (+"," (")&amp;FIXED(Painel!D14*100,0)&amp;"% em relação a "&amp;Config!$B$8&amp;")","")&amp;IF(Painel!E14&lt;&gt;"","; meta "&amp;IF(Indicadores!B14="R$","R$ ","")&amp;FIXED(Painel!E14,IF(Indicadores!C14="",0,Indicadores!C14))&amp;IF(OR(Indicadores!B14="R$",Indicadores!B14=""),""," "&amp;Indicadores!B14)&amp;", "&amp;LOWER(Painel!G14),"")&amp;".")</f>
+        <f>IF(OR(Indicadores!A14="",Painel!B14=""),"","• "&amp;Indicadores!A14&amp;": "&amp;IF(Indicadores!B14="R$","R$ ","")&amp;FIXED(Painel!B14,IF(Indicadores!C14="",0,Indicadores!C14))&amp;IF(OR(Indicadores!B14="R$",Indicadores!B14=""),""," "&amp;Indicadores!B14)&amp;IF(Painel!C14="","",IF(AND(Painel!C14=0,Painel!B14&lt;&gt;0)," (sem base de comparação: "&amp;Config!$B$8&amp;" foi zero)",IF(Painel!D14="","",IF(Painel!D14&gt;=0," (+"," (")&amp;FIXED(Painel!D14*100,0)&amp;"% em relação a "&amp;Config!$B$8&amp;")")))&amp;IF(Painel!E14&lt;&gt;"","; meta "&amp;IF(Indicadores!B14="R$","R$ ","")&amp;FIXED(Painel!E14,IF(Indicadores!C14="",0,Indicadores!C14))&amp;IF(OR(Indicadores!B14="R$",Indicadores!B14=""),""," "&amp;Indicadores!B14)&amp;", "&amp;LOWER(Painel!G14),"")&amp;".")</f>
         <v>• NPS: 72 pts (-1% em relação a Agosto); meta 70 pts, no alvo.</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="19" t="str">
-        <f>IF(OR(Indicadores!A15="",Painel!B15=""),"","• "&amp;Indicadores!A15&amp;": "&amp;IF(Indicadores!B15="R$","R$ ","")&amp;FIXED(Painel!B15,IF(Indicadores!C15="",0,Indicadores!C15))&amp;IF(OR(Indicadores!B15="R$",Indicadores!B15=""),""," "&amp;Indicadores!B15)&amp;IF(Painel!C15&lt;&gt;"",IF(Painel!D15&gt;=0," (+"," (")&amp;FIXED(Painel!D15*100,0)&amp;"% em relação a "&amp;Config!$B$8&amp;")","")&amp;IF(Painel!E15&lt;&gt;"","; meta "&amp;IF(Indicadores!B15="R$","R$ ","")&amp;FIXED(Painel!E15,IF(Indicadores!C15="",0,Indicadores!C15))&amp;IF(OR(Indicadores!B15="R$",Indicadores!B15=""),""," "&amp;Indicadores!B15)&amp;", "&amp;LOWER(Painel!G15),"")&amp;".")</f>
+        <f>IF(OR(Indicadores!A15="",Painel!B15=""),"","• "&amp;Indicadores!A15&amp;": "&amp;IF(Indicadores!B15="R$","R$ ","")&amp;FIXED(Painel!B15,IF(Indicadores!C15="",0,Indicadores!C15))&amp;IF(OR(Indicadores!B15="R$",Indicadores!B15=""),""," "&amp;Indicadores!B15)&amp;IF(Painel!C15="","",IF(AND(Painel!C15=0,Painel!B15&lt;&gt;0)," (sem base de comparação: "&amp;Config!$B$8&amp;" foi zero)",IF(Painel!D15="","",IF(Painel!D15&gt;=0," (+"," (")&amp;FIXED(Painel!D15*100,0)&amp;"% em relação a "&amp;Config!$B$8&amp;")")))&amp;IF(Painel!E15&lt;&gt;"","; meta "&amp;IF(Indicadores!B15="R$","R$ ","")&amp;FIXED(Painel!E15,IF(Indicadores!C15="",0,Indicadores!C15))&amp;IF(OR(Indicadores!B15="R$",Indicadores!B15=""),""," "&amp;Indicadores!B15)&amp;", "&amp;LOWER(Painel!G15),"")&amp;".")</f>
         <v>• Horas extras da equipe: 12 h (-14% em relação a Agosto); meta 20 h, no alvo.</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="19" t="str">
-        <f>IF(OR(Indicadores!A16="",Painel!B16=""),"","• "&amp;Indicadores!A16&amp;": "&amp;IF(Indicadores!B16="R$","R$ ","")&amp;FIXED(Painel!B16,IF(Indicadores!C16="",0,Indicadores!C16))&amp;IF(OR(Indicadores!B16="R$",Indicadores!B16=""),""," "&amp;Indicadores!B16)&amp;IF(Painel!C16&lt;&gt;"",IF(Painel!D16&gt;=0," (+"," (")&amp;FIXED(Painel!D16*100,0)&amp;"% em relação a "&amp;Config!$B$8&amp;")","")&amp;IF(Painel!E16&lt;&gt;"","; meta "&amp;IF(Indicadores!B16="R$","R$ ","")&amp;FIXED(Painel!E16,IF(Indicadores!C16="",0,Indicadores!C16))&amp;IF(OR(Indicadores!B16="R$",Indicadores!B16=""),""," "&amp;Indicadores!B16)&amp;", "&amp;LOWER(Painel!G16),"")&amp;".")</f>
+        <f>IF(OR(Indicadores!A16="",Painel!B16=""),"","• "&amp;Indicadores!A16&amp;": "&amp;IF(Indicadores!B16="R$","R$ ","")&amp;FIXED(Painel!B16,IF(Indicadores!C16="",0,Indicadores!C16))&amp;IF(OR(Indicadores!B16="R$",Indicadores!B16=""),""," "&amp;Indicadores!B16)&amp;IF(Painel!C16="","",IF(AND(Painel!C16=0,Painel!B16&lt;&gt;0)," (sem base de comparação: "&amp;Config!$B$8&amp;" foi zero)",IF(Painel!D16="","",IF(Painel!D16&gt;=0," (+"," (")&amp;FIXED(Painel!D16*100,0)&amp;"% em relação a "&amp;Config!$B$8&amp;")")))&amp;IF(Painel!E16&lt;&gt;"","; meta "&amp;IF(Indicadores!B16="R$","R$ ","")&amp;FIXED(Painel!E16,IF(Indicadores!C16="",0,Indicadores!C16))&amp;IF(OR(Indicadores!B16="R$",Indicadores!B16=""),""," "&amp;Indicadores!B16)&amp;", "&amp;LOWER(Painel!G16),"")&amp;".")</f>
         <v>• Custo por lead: R$ 40,70 (+3% em relação a Agosto); meta R$ 45,00, no alvo.</v>
       </c>
     </row>
